--- a/data/processed/기후환경_행정기구_현황.xlsx
+++ b/data/processed/기후환경_행정기구_현황.xlsx
@@ -10,7 +10,7 @@
     <sheet name="기후환경 행정기구 현황" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'기후환경 행정기구 현황'!$A$1:$R$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'기후환경 행정기구 현황'!$A$1:$W$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4692,6 +4692,27 @@
 7. 30.)(제9조에서 이동</t>
       </text>
     </comment>
+    <comment ref="E60" authorId="0" shapeId="0">
+      <text>
+        <t>1. 환경보전 종합계획 수립추진에 관한 사항
+2. 자연생태, 기후변화대응에 관한 사항
+3. 먹는물, 지하수 등 수질관리 업무에 관한 사항 &lt;신설 2025.12.29.&gt;
+4. 하수도 시설 설치 및 관리에 관한 사항
+5. 분뇨ㆍ폐수처리장 설치 및 운영에 관한 사항
+6. 배출시설 지도점검 및 행정처분
+7. 오염총량관리제 시행관련 업무
+8. 환경시설 관리 및 폐기물 처리, 생활쓰레기 관리에 관한 업무</t>
+      </text>
+    </comment>
+    <comment ref="E61" authorId="0" shapeId="0">
+      <text>
+        <t>1. 산림경영 및 보호에 관한 사항
+2. 산림문화ㆍ휴양시설 조성 및 운영
+3. 새마을사업 종합추진에 관한 사항
+4. 광고물, 읍ㆍ면 복지회관 관리ㆍ운영 등에 관한 사항
+5. 그 밖에 산림새마을행정 업무에 관한 사항</t>
+      </text>
+    </comment>
     <comment ref="E62" authorId="0" shapeId="0">
       <text>
         <t>1. 재난ㆍ안전정책의 총괄 및 조정에 관한 사항
@@ -7981,6 +8002,36 @@
 41. 그 밖의 관광·문화체육·지역산업·농업정책·유통축산·환경·산림·건설·도시행정에 관한 사항</t>
       </text>
     </comment>
+    <comment ref="E159" authorId="0" shapeId="0">
+      <text>
+        <t>1. 환경정책의 계획수립 및 총괄기획ㆍ조정에 관한 사항
+2. 환경보전에 관한 지도 및 홍보에 관한 사항
+3. 야생동물보호 및 유해조수 퇴치에 관한 사항
+4. 대규모 축사, 악취 등 청정환경 추진에 관한 사항
+5. 수질오염총량제 등 수질보존 종합대책 수립 및 시행에 관한 사항
+6. 지하수업무 전반에 관한 사항
+7. 생활환경에 관한 사항
+8. 폐기물처리 및 관리에 관한 사항
+9. 두루미 생태 환경 보존에 관한 사항
+10. 국제두루미 센터 및 야생조수류보호사 관리에 관한 사항 &lt;신설 2022. 12. 14.&gt;
+11. 두루미 관련 보호 단체 육성 및 지원에 관한 사항 &lt;신설 2022. 12. 14.&gt;
+12. 국가생태습지보호지역의 지정 및 운영에 관한 사항 &lt;신설 2022. 12. 14.&gt;
+13. 환경 위해 외래 동식물 제거사업의 추진에 관한 사항 &lt;신설 2022. 12. 14.&gt;</t>
+      </text>
+    </comment>
+    <comment ref="E160" authorId="0" shapeId="0">
+      <text>
+        <t>1. 산림정책 총괄 조정, 지역산림계획 수립 및 조정에 관한 사항
+2. &lt;삭제 2022. 12. 14.&gt;
+3. 산불예방 및 산림내 위ㆍ불법행위 단속 등 산림보호에 관한 사항
+4. 산지이용에 관한 사항
+5. 임산물의 소득증대 대책 수립 및 실행
+6. 조림, 숲가꾸기, 사방, 임도, 산사태 방지 및 군유림관리에 관한 사항 &lt;개정 2022. 12. 14.&gt;
+7. 도시숲 등 조성ㆍ관리 계획 수립 및 녹지공간 운영관리에 관한 사항 &lt;개정 2022. 12. 14.&gt;
+8. 목재문화체험장, 두루웰 숲속문화촌, 캠핑장 운영 및 관리에 관한 사항 &lt;개정 2022. 12. 14.&gt;
+9. 가로수 등 조성, 관리 계획 수립 및 유지관리에 관한 사항 &lt;개정 2022. 12. 14.&gt;</t>
+      </text>
+    </comment>
     <comment ref="E163" authorId="0" shapeId="0">
       <text>
         <t>1. 국의 행정사무를 분장하게 하기 위하여 행정복지국에 자치행정과, 민원서비스과, 평생교육과, 사회복지과, 환경과, 세무회계과를 둔
@@ -10232,7 +10283,69 @@
 5. 민원행정, 주민등록, 여권, 가족관계사무, 정보공개, 부동산 관리, 지적재조사, 공간정보 등에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E255" authorId="0" shapeId="0">
+    <comment ref="E245" authorId="0" shapeId="0">
+      <text>
+        <t>1. 산지이용 구분 및 기본계획 수립
+2. 조림사업 및 숲가꾸기 사업 시행
+3. 산림경영계획 수립 및 인가
+4. 임목벌채 등의 허가 및 신고
+5. 산촌생태마을 조성 및 사후관리
+6. 산림재해 총괄대책 수립
+7. 산림소득사업 전반
+8. 목재산업 육성
+9. 산림병해충 예찰 및 방제
+10. 산불예방 및 진화
+11. 숲길조성 및 유지관리
+12. 지리산둘레길 관리
+13. 백두대간 보호 및 주민소득사업 지원
+14. 산림보호단속 및 산림피해 특별사법 관리거. 공유림 관리너. 도시숲, 소공원 및 가로화단 조성·관리더. 사방사업 시행 및 관리러. 임도시설사업 추진머. 도시산림공원 조성 및 관리</t>
+      </text>
+    </comment>
+    <comment ref="E246" authorId="0" shapeId="0">
+      <text>
+        <t>1. 환경보전 종합계획수립·시행
+2. 환경영향평가 협의 및 환경분쟁 조정
+3. 폐기물 처리에 관한 사항
+4. 쓰레기 종량제 업무 및 매립장 관리
+5. 자원순환에 관한 사항
+6. 환경 인·허가
+7. 환경오염시설 지도·단속
+8. 야생 동·식물 보호
+9. 국립공원 관련 업무
+10. 삭제 &lt;2023. 1. 9.&gt;
+11. 삭제 &lt;2023. 1. 9.&gt;</t>
+      </text>
+    </comment>
+    <comment ref="E249" authorId="0" shapeId="0">
+      <text>
+        <t>1. 환경보전 종합계획 수립 지도
+2. 환경영향평가 업무
+3. 오염물질배출 사업장 지도·점검
+4. 오수ㆍ분뇨ㆍ가축분뇨 처리시설 지도·점검
+5. 친환경자동차 보급사업(전기·수소자동차, 충전소 등)
+6. 주암호 수질관리
+7. 쓰레기 종량제 추진
+8. 폐기물 처리업 인ㆍ허가 및 지도·점검
+9. 쓰레기 소각장ㆍ매립장 시설 설치 및 운영관리
+10. 공중화장실 시설 유지관리
+11. 유해 야생동식물 업무 추진
+12. 기후변화 대응 관련 종합계획 수립 및 추진</t>
+      </text>
+    </comment>
+    <comment ref="E250" authorId="0" shapeId="0">
+      <text>
+        <t>1. 양묘ㆍ조림사업 시행ㆍ지도
+2. 산지 자원화 계획 수립 시행
+3. 산림형질변경 및 토ㆍ사석 채취허가
+4. 산불방지 종합대책 수립 및 예방 홍보
+5. 산림휴양 시설 관리
+6. 가로수 식재 관리
+7. 산림경영계획 산림사업 신고 수리
+8. 산림생태문화체험단지 조성 및 운영관리
+9. 전남권환경성질환예방관리센터 운영관리</t>
+      </text>
+    </comment>
+    <comment ref="E254" authorId="0" shapeId="0">
       <text>
         <t>1. 농업행정, 친환경농업, 원예특작, 유통, 농식품산업 전반에 관한 사항
 2. 산림경영, 산림관리, 산림휴양, 공원 전반에 관한 사항
@@ -10240,7 +10353,7 @@
 4. 해양개발, 수산진흥, 해양레저관광, 생태공원 전반에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E256" authorId="0" shapeId="0">
+    <comment ref="E255" authorId="0" shapeId="0">
       <text>
         <t>1. 복지정책, 희망복지, 통합조사, 장애인복지 전반에 관한 사항
 2. 노인, 여성, 아동, 청소년 전반에 관한 사항
@@ -10248,7 +10361,7 @@
 4. 일반ㆍ복합민원, 건축, 지적, 지적재조사, 토지관리 전반에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E259" authorId="0" shapeId="0">
+    <comment ref="E258" authorId="0" shapeId="0">
       <text>
         <t>1. 농업정책, 친환경농업육성, 농업지원, 농지관리, 농산물 유통, 농식품산업 등에 관한 사항
 2. 축산정책, 가축방역, 동물복지, 해양·수산행정 등에 관한 사항
@@ -10257,13 +10370,35 @@
 5. 기업투자유치, 대불산단 기업 지원 및 산단 대개조, 기업도시 지원 및 종합계획 수립 등에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E260" authorId="0" shapeId="0">
+    <comment ref="E259" authorId="0" shapeId="0">
       <text>
         <t>1. 안전정책, 사회재난, 자연재난, 하천관리, 중대재해예방, 통합관제, 민방위 상시재난상황실 운영 등에 관한 사항
 2. 건설행정, 도로관리, 농업기반시설, 교통행정, 교통시설, 교통민원, 차량등록 등에 관한 사항
 3. 도시계획 및 개발, 도시시설, 도시경관, 도시재생, 건축지도, 공동주택, 농촌개발 등에 관한 사항
 4. 환경정책, 생태, 환경지도, 기후대기, 환경시설, 생활폐기물 등에 관한 사항
 5. 공영개발 종합계획 수립, 건축시설 공사에 관한 사항</t>
+      </text>
+    </comment>
+    <comment ref="E260" authorId="0" shapeId="0">
+      <text>
+        <t>1. 환경보전 및 관리, 미화, 지도 등 환경에 관한 사항
+2. 야생동식물, 지하수, 폐기물, 기후변화 대응에 관한 사항</t>
+      </text>
+    </comment>
+    <comment ref="E261" authorId="0" shapeId="0">
+      <text>
+        <t>1. 산림 조림, 보호, 조경에 관한 사항
+2. 가로수, 공원관리에 관한 사항</t>
+      </text>
+    </comment>
+    <comment ref="E264" authorId="0" shapeId="0">
+      <text>
+        <t>1. 상·하수도 종합계획 수립·조정 및 시행
+2. 지방상수도 설치 및 수질관리
+3. 상수도 시설물 유지관리 및 운영
+4. 공공하수도 설치 및 관리
+5. 공공하수처리시설 운영 관리
+6. 생활하수, 가축분뇨, 분뇨 등 위생적 종합 처리</t>
       </text>
     </comment>
     <comment ref="E267" authorId="0" shapeId="0">
@@ -10821,7 +10956,33 @@
 7. 기타 하수ㆍ분뇨ㆍ축산폐수의 위생적 처리, 상ㆍ하수시설 관리에 관계되는 사항</t>
       </text>
     </comment>
-    <comment ref="E274" authorId="0" shapeId="0">
+    <comment ref="E271" authorId="0" shapeId="0">
+      <text>
+        <t>1. 환경정책 업무에 관한 사항
+2. 환경보호 및 폐기물 관리 업무에 관한 사항
+3. 환경관리센터 업무 및 생활폐기물 처리에 관한 사항
+4. 상수도 및 마을상수도 개발ㆍ관리에 관한 사항
+5. 분뇨위생처리에 관한 사항
+6. 하수도시설 개발ㆍ관리에 관한 사항
+7. 하수종말처리장 시설관리에 관한 사항
+8. 마을하수처리장 및 기반시설 관리에 관한 사항
+9. 분뇨처리 및 수질관리에 관한 사항
+10. 하수관거 시설 개발ㆍ관리에 관한 사항
+11. 상ㆍ하수도 사용료 부과징수에 관한 사항
+12. 그 밖의 환경, 상·하수도 업무에 관한 사항</t>
+      </text>
+    </comment>
+    <comment ref="E272" authorId="0" shapeId="0">
+      <text>
+        <t>1. 산림 정책 및 경영 업무에 관한 사항
+2. 조림사업에 관한 사항
+3. 산림보호를 위한 지도ㆍ단속에 관한 사항
+4. 산지관리에 관한 사항
+5. 자연휴양림 조성 등 산림휴양에 관한 사항
+6. 그 밖의 산림 업무에 관한 사항</t>
+      </text>
+    </comment>
+    <comment ref="E273" authorId="0" shapeId="0">
       <text>
         <t>1. 13.,
 2. 농업정책 및 농업생산·소득증대·친환경농업·식량원예에 관한 사항 (개정
@@ -10832,7 +10993,7 @@
 7. 농어촌 마을 정비 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E275" authorId="0" shapeId="0">
+    <comment ref="E274" authorId="0" shapeId="0">
       <text>
         <t>1. 해양수산정책에 관한 사항
 2. 해양레저 및 섬개발 행정에 관한 사항 (개정
@@ -10844,7 +11005,7 @@
 8. 2012 여수세계박람회 사후활용에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E276" authorId="0" shapeId="0">
+    <comment ref="E275" authorId="0" shapeId="0">
       <text>
         <t>1. 환경 보전에 관한 종합계획 수립 및 추진
 2. 대기환경ㆍ수질환경 보전에 관한 사항
@@ -10856,7 +11017,7 @@
 8. 그 밖의 환경 및 산림 관련 업무 전반에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E277" authorId="0" shapeId="0">
+    <comment ref="E276" authorId="0" shapeId="0">
       <text>
         <t>1. 환경행정의 종합 기획 및 추진
 2. 환경보전 종합계획수립 등 환경보호 업무
@@ -10865,7 +11026,7 @@
 5. [본조 신설 2017.6.7.][제목 개정 2020.5.26.]</t>
       </text>
     </comment>
-    <comment ref="F277" authorId="0" shapeId="0">
+    <comment ref="F276" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보전 종합계획 수립
 2. 환경영향평가 협의
@@ -10886,7 +11047,7 @@
 17. 군용비행장 및 군사격장 소음피해에 따른 보상 처리에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="G277" authorId="0" shapeId="0">
+    <comment ref="G276" authorId="0" shapeId="0">
       <text>
         <t>1. 기후변화대응 종합계획 수립
 2. 탄소중립 정책 추진 및 온실가스 감축 관련 업무
@@ -10897,7 +11058,7 @@
 7. 친환경자동차 보급 업무 관리[본조신설 2024.6.26.]</t>
       </text>
     </comment>
-    <comment ref="H277" authorId="0" shapeId="0">
+    <comment ref="H276" authorId="0" shapeId="0">
       <text>
         <t>1. 청소행정ㆍ자원순환 정책 수립 및 추진
 2. 생활폐기물 수집ㆍ운반 및 처리에 관한 종합계획
@@ -10918,7 +11079,7 @@
 17. 생활폐기물 매립장 총괄관리 및 운영</t>
       </text>
     </comment>
-    <comment ref="I277" authorId="0" shapeId="0">
+    <comment ref="I276" authorId="0" shapeId="0">
       <text>
         <t>1. 식품정책 및 위생행정의 종합계획 수립
 2. 식품위생 및 공중위생 제도 개선
@@ -10937,7 +11098,7 @@
 15. 푸드테크산업 육성 및 지원</t>
       </text>
     </comment>
-    <comment ref="E278" authorId="0" shapeId="0">
+    <comment ref="E277" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보호업무에 관한 사항
 2. 청소행정 및 자원 순환에 관한 사항
@@ -10948,7 +11109,7 @@
 7. 사적관리사무소 지도ㆍ감독에 관한 사항[본조신설 2024.7.1.][종전 제10조는 제12조로 이동 ]</t>
       </text>
     </comment>
-    <comment ref="F278" authorId="0" shapeId="0">
+    <comment ref="F277" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보호 종합계획 수립시행
 2. 환경영향평가에 관한 사항
@@ -10978,7 +11139,7 @@
 26. 그 밖의 환경보호와 관련된 사항[제목개정 2023.12.28.][제21조에서 이동 ]</t>
       </text>
     </comment>
-    <comment ref="G278" authorId="0" shapeId="0">
+    <comment ref="G277" authorId="0" shapeId="0">
       <text>
         <t>1. 폐기물처리에 관한 종합계획 수립시행
 2. 폐기물처리 허가 및 지도감독
@@ -11002,7 +11163,7 @@
 20. 그 밖의 청소, 자원재생 및 순환에 관한 사항[본조신설 2024.7.1.][종전의 제46조는 제57조로 이동 ]</t>
       </text>
     </comment>
-    <comment ref="H278" authorId="0" shapeId="0">
+    <comment ref="H277" authorId="0" shapeId="0">
       <text>
         <t>1. 임야 내 치산계획 수립 및 실시
 2. 양묘 및 조림사업 시행지도
@@ -11020,7 +11181,7 @@
 14. 그 밖의 산림 업무에 관한 사항[제20조에서 이동 2018.8.31.][제22조의7에서 이동 ][제22조의8에서 이동 ]</t>
       </text>
     </comment>
-    <comment ref="I278" authorId="0" shapeId="0">
+    <comment ref="I277" authorId="0" shapeId="0">
       <text>
         <t>1. 도시공원 조성에 관한 사항
 2. 도시 공간, 녹화사업의 종합계획
@@ -11033,7 +11194,7 @@
 9. 그 밖의 도시 공간 녹지 조경에 관한 사항[본조신설 2024.7.1.][종전의 제48조는 제59조로 이동 ]</t>
       </text>
     </comment>
-    <comment ref="J278" authorId="0" shapeId="0">
+    <comment ref="J277" authorId="0" shapeId="0">
       <text>
         <t>1. 지적업무 기획 및 조정
 2. 지적민원 처리
@@ -11059,7 +11220,7 @@
 22. 그 밖의 지적업무에 관한 사항[제30조에서 이동 ]</t>
       </text>
     </comment>
-    <comment ref="E279" authorId="0" shapeId="0">
+    <comment ref="E278" authorId="0" shapeId="0">
       <text>
         <t>1. 기후변화대응 종합계획 수립ㆍ조정
 2. 에너지 정책 종합 기획ㆍ조정
@@ -11074,7 +11235,7 @@
 11. 청소행정의 종합계획 수립ㆍ조정</t>
       </text>
     </comment>
-    <comment ref="F279" authorId="0" shapeId="0">
+    <comment ref="F278" authorId="0" shapeId="0">
       <text>
         <t>1. 국 소관 행정의 종합기획ㆍ조정
 2. 기후변화대응 총괄계획 수립
@@ -11088,7 +11249,7 @@
 10. 그 밖에 공원관리에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="G279" authorId="0" shapeId="0">
+    <comment ref="G278" authorId="0" shapeId="0">
       <text>
         <t>1. 산림경영계획에 관한 사항
 2. 입목의 벌채신고ㆍ허가에 관한 사항
@@ -11106,7 +11267,7 @@
 14. 산림재해 예방 및 복구에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="H279" authorId="0" shapeId="0">
+    <comment ref="H278" authorId="0" shapeId="0">
       <text>
         <t>1. 상하수도 행정의 종합 기획ㆍ조정
 2. 상하수도 사용료 부과ㆍ징수
@@ -11121,7 +11282,7 @@
 11. 맑은물사업소 지도ㆍ감독</t>
       </text>
     </comment>
-    <comment ref="I279" authorId="0" shapeId="0">
+    <comment ref="I278" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보전 종합계획 수립
 2. 환경개선부담금에 관한 사항
@@ -11142,7 +11303,7 @@
 17. 어린이급식관리지원센터 운영에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="J279" authorId="0" shapeId="0">
+    <comment ref="J278" authorId="0" shapeId="0">
       <text>
         <t>1. 환경기초시설 공사 및 관리감독
 2. 공중화장실 점검 및 관리
@@ -11157,7 +11318,7 @@
 11. 영농폐기물 수거 및 관리</t>
       </text>
     </comment>
-    <comment ref="E280" authorId="0" shapeId="0">
+    <comment ref="E279" authorId="0" shapeId="0">
       <text>
         <t>1. 수자원정책에 관한 사항
 2. 환경관리 및 청소ㆍ자원순환에 관한 사항
@@ -11166,7 +11327,7 @@
 5. 안동임하호수운관리사무소 운영 지도ㆍ감독</t>
       </text>
     </comment>
-    <comment ref="F280" authorId="0" shapeId="0">
+    <comment ref="F279" authorId="0" shapeId="0">
       <text>
         <t>1. 국 소관 행정의 종합ㆍ조정
 2. 수자원정책과 행정의 종합기획
@@ -11192,7 +11353,7 @@
 22. 낙동강살리기 어린이물놀이장 조성 및 관리</t>
       </text>
     </comment>
-    <comment ref="G280" authorId="0" shapeId="0">
+    <comment ref="G279" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보전 종합계획 수립ㆍ조정
 2. 자연환경보전에 관한 사항
@@ -11252,7 +11413,7 @@
 56. 그 밖에 환경ㆍ수질업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="H280" authorId="0" shapeId="0">
+    <comment ref="H279" authorId="0" shapeId="0">
       <text>
         <t>1. 폐기물처리업 및 처리시설허가 및 승인에 관한 사항
 2. 폐기물(생활폐기물, 사업장폐기물 등)에 관한 사항
@@ -11282,7 +11443,7 @@
 26. 그 밖에 청소 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="I280" authorId="0" shapeId="0">
+    <comment ref="I279" authorId="0" shapeId="0">
       <text>
         <t>1. 산림종합개발 계획수립 및 산림경영계획 운영에 관한 사항
 2. 조림 육림 양묘 계획수립 및 사후관리
@@ -11313,7 +11474,7 @@
 27. 산촌개발사업 추진</t>
       </text>
     </comment>
-    <comment ref="J280" authorId="0" shapeId="0">
+    <comment ref="J279" authorId="0" shapeId="0">
       <text>
         <t>1. 공원녹지기본계획 수립
 2. 도시공원 및 녹지 조성
@@ -11348,7 +11509,7 @@
 31. 도시계획시설(공원)사업 실시계획인가</t>
       </text>
     </comment>
-    <comment ref="E281" authorId="0" shapeId="0">
+    <comment ref="E280" authorId="0" shapeId="0">
       <text>
         <t>1. 맑은물정책에 관한 사항
 2. 상ㆍ하수도에 관한 사항
@@ -11356,7 +11517,7 @@
 4. 상수원 보호구역관리에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="F281" authorId="0" shapeId="0">
+    <comment ref="F280" authorId="0" shapeId="0">
       <text>
         <t>1. 국 소관 행정의 종합ㆍ조정
 2. 상하수도 행정의 기획, 조정, 조례관리
@@ -11377,7 +11538,7 @@
 17. 지방채, 기채, 일시차입금, 채무부담행위에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="G281" authorId="0" shapeId="0">
+    <comment ref="G280" authorId="0" shapeId="0">
       <text>
         <t>1. 수도정비기본계획 수립 및 변경사항
 2. 물 수요관리 시행계획 수립 및 변경사항
@@ -11397,7 +11558,7 @@
 16. 상수도원인자부담금 부과 및 징수</t>
       </text>
     </comment>
-    <comment ref="H281" authorId="0" shapeId="0">
+    <comment ref="H280" authorId="0" shapeId="0">
       <text>
         <t>1. 하수도정비 기본계획수립 및 변경사항
 2. 하수도 시설의 설치 및 유지관리에 관한 사항
@@ -11417,7 +11578,7 @@
 16. 하수처리시설 대행사업비 편성, 지급, 정산</t>
       </text>
     </comment>
-    <comment ref="I281" authorId="0" shapeId="0">
+    <comment ref="I280" authorId="0" shapeId="0">
       <text>
         <t>1. 상수원 보호구역관리
 2. 상수원보호구역 수질관리계획 수립ㆍ시행
@@ -11436,7 +11597,7 @@
 15. 그 밖에 맑은물관리과 운영에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E282" authorId="0" shapeId="0">
+    <comment ref="E281" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보전계획 수립 및 추진에 관한 사항
 2. 대기환경관리계획 및 실행에 관한 사항
@@ -11450,7 +11611,7 @@
 10. 매립장 및 환경자원화 시설물 설치 및 관리운영[제11조에서 이동]</t>
       </text>
     </comment>
-    <comment ref="F282" authorId="0" shapeId="0">
+    <comment ref="F281" authorId="0" shapeId="0">
       <text>
         <t>1. 국ㆍ과 소관 행정 종합기획 및 조정
 2. 환경정책기획 및 환경보전계획 수립 추진
@@ -11472,7 +11633,7 @@
 18. 그 밖에 다른 국 내 다른 과에 속하지 아니하는 사항</t>
       </text>
     </comment>
-    <comment ref="G282" authorId="0" shapeId="0">
+    <comment ref="G281" authorId="0" shapeId="0">
       <text>
         <t>1. 환경안전 기본계획 수립 및 관리에 관한 사항
 2. 환경기술인단체관리 및 지원에 관한 사항
@@ -11498,7 +11659,7 @@
 22. 공공폐수처리시설 관리에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="H282" authorId="0" shapeId="0">
+    <comment ref="H281" authorId="0" shapeId="0">
       <text>
         <t>1. 교통정책 종합기획 수립 및 추진
 2. 도시교통사업특별회계의 운영 및 관리
@@ -11520,7 +11681,7 @@
 18. 그 밖에 교통정책에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="I282" authorId="0" shapeId="0">
+    <comment ref="I281" authorId="0" shapeId="0">
       <text>
         <t>1. 대중교통 기본계획 수립 및 추진
 2. 시내버스에 관한 사항
@@ -11536,7 +11697,7 @@
 12. 그 밖에 사업용운수차량에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="J282" authorId="0" shapeId="0">
+    <comment ref="J281" authorId="0" shapeId="0">
       <text>
         <t>1. 도립공원 기본계획수립 시행
 2. 도립공원 기반조성
@@ -11557,7 +11718,7 @@
 17. 그 밖에 도시공원 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="K282" authorId="0" shapeId="0">
+    <comment ref="K281" authorId="0" shapeId="0">
       <text>
         <t>1. 자원순환 집행계획 수립 추진
 2. 생활폐기물 처리 관련 업무
@@ -11578,7 +11739,7 @@
 17. 환경자원화시설 관련 주민편익 사업</t>
       </text>
     </comment>
-    <comment ref="E283" authorId="0" shapeId="0">
+    <comment ref="E282" authorId="0" shapeId="0">
       <text>
         <t>1. 지역경제 활성화 대책 추진 및 일자리 창출 추진에 관한 사항
 2. 전통시장 및 상점가 시설개선사업에 관한 사항
@@ -11599,7 +11760,7 @@
 17. 도시공간 녹화 및 국토공원화사업 추진에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E284" authorId="0" shapeId="0">
+    <comment ref="E283" authorId="0" shapeId="0">
       <text>
         <t>1. 지역 일자리 창출에 관한 사항
 2. 지역경제 활성화를 위한 종합기획ㆍ조정
@@ -11614,7 +11775,7 @@
 11. 산림보호 및 국ㆍ공유 임야 재산관리 [제목개정 2018.5.11., 2020.4.10.]</t>
       </text>
     </comment>
-    <comment ref="F284" authorId="0" shapeId="0">
+    <comment ref="F283" authorId="0" shapeId="0">
       <text>
         <t>1. 지역단위 경제의 종합기획조정
 2. 지역공동체 일자리 사업 추진 관리
@@ -11631,7 +11792,7 @@
 13. 그 밖에 국에서 다른 과에 속하지 아니하는 사항 [본조 신설 2014.12.31]</t>
       </text>
     </comment>
-    <comment ref="G284" authorId="0" shapeId="0">
+    <comment ref="G283" authorId="0" shapeId="0">
       <text>
         <t>1. 기업 유치에 관한 사항
 2. 경영수익사업 종합계획 수립 및 분석ㆍ조정
@@ -11648,7 +11809,7 @@
 13. 산업단지 조성에 관한 사항 [본조 신설 2015.07.01][제22조의5에서 이동 ][제목개정 2018.5.11.&gt;]</t>
       </text>
     </comment>
-    <comment ref="H284" authorId="0" shapeId="0">
+    <comment ref="H283" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보전 종합계획 수립 시행
 2. 환경관련 위원회 운영
@@ -11666,7 +11827,7 @@
 14. 축산폐수 행정에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="I284" authorId="0" shapeId="0">
+    <comment ref="I283" authorId="0" shapeId="0">
       <text>
         <t>1. 음식물류폐기물 수거운반 및 처리에 관한 사항
 2. 쓰레기종량제 및 1회용품 사용억제사업 추진
@@ -11683,7 +11844,7 @@
 13. 사업장 배출시 설계 및 사업장생활계 수집업 허가 및 신고 [제목개정 2017.7.1.]</t>
       </text>
     </comment>
-    <comment ref="J284" authorId="0" shapeId="0">
+    <comment ref="J283" authorId="0" shapeId="0">
       <text>
         <t>1. 산림경영계획의 수립 시행
 2. 양묘, 종묘 생산관리
@@ -11705,7 +11866,7 @@
 18. 기타 산림업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E285" authorId="0" shapeId="0">
+    <comment ref="E284" authorId="0" shapeId="0">
       <text>
         <t>1. 국 소관 행정의 종합기획 조정
 2. 지역단위 경제의 종합기획 조정
@@ -11740,7 +11901,7 @@
 31. 휴양림에 관한 사항 [전문개정 2011.1.10]</t>
       </text>
     </comment>
-    <comment ref="F285" authorId="0" shapeId="0">
+    <comment ref="F284" authorId="0" shapeId="0">
       <text>
         <t>1. 지역경제에 관한 종합기획 조정
 2. 물가종합대책 수립 추진
@@ -11767,7 +11928,7 @@
 23. 그 밖에 국내 다른 과에 속하지 아니하는 사항[전문개정 2011.1.10, 2014.9.19, 2015.1.14][제목개정 2022.12.30.]</t>
       </text>
     </comment>
-    <comment ref="G285" authorId="0" shapeId="0">
+    <comment ref="G284" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보전종합계획 수립 추진
 2. 기후변화 및 탄소중립에 관한 사항
@@ -11793,7 +11954,7 @@
 22. 그 밖에 환경관리에 관한 사항[전문개정 2024.12.31.]</t>
       </text>
     </comment>
-    <comment ref="H285" authorId="0" shapeId="0">
+    <comment ref="H284" authorId="0" shapeId="0">
       <text>
         <t>1. 농정행정의 종합기획 조정
 2. 농어촌발전 중장기계획 수립 및 추진
@@ -11826,7 +11987,7 @@
 29. 그 밖에 농업정책에 관한 사항[전문개정 2011.1.10]</t>
       </text>
     </comment>
-    <comment ref="I285" authorId="0" shapeId="0">
+    <comment ref="I284" authorId="0" shapeId="0">
       <text>
         <t>1. 스마트 팜 혁신밸리 조성 및 운영 계획 수립에 관한 사항
 2. 스마트 팜 혁신밸리 조성을 위한 행정절차 추진에 관한 사항
@@ -11840,7 +12001,7 @@
 10. 그 밖에 스마트팜 혁신밸리 운영에 관한 사항[본조신설 2018.12.3.][제목개정 2021.12.31., 2022.12.30.]</t>
       </text>
     </comment>
-    <comment ref="J285" authorId="0" shapeId="0">
+    <comment ref="J284" authorId="0" shapeId="0">
       <text>
         <t>1. 축산진흥의 종합기획 조정
 2. 가축개량에 관한 사항
@@ -11863,7 +12024,7 @@
 19. 그 밖에 축산에 관한 사항[전문개정 2011.1.10][제목개정 2015.1.14, 2018.12.3.&gt;</t>
       </text>
     </comment>
-    <comment ref="K285" authorId="0" shapeId="0">
+    <comment ref="K284" authorId="0" shapeId="0">
       <text>
         <t>1. 농산물 유통의 종합기획 조정
 2. 농산물 가공·처리·유통에 관한 사항
@@ -11880,7 +12041,7 @@
 13. 그 밖에 유통마케팅에 관한 사항[본조신설 2015.1.14]</t>
       </text>
     </comment>
-    <comment ref="L285" authorId="0" shapeId="0">
+    <comment ref="L284" authorId="0" shapeId="0">
       <text>
         <t>1. 산림행정의 종합기획 조정
 2. 치산계획의 수립 및 시행
@@ -11905,7 +12066,7 @@
 21. 그 밖에 산림녹지에 관한 사항[전문개정 2011.1.10][제목개정 2015.1.14]</t>
       </text>
     </comment>
-    <comment ref="E286" authorId="0" shapeId="0">
+    <comment ref="E285" authorId="0" shapeId="0">
       <text>
         <t>1. 문화예술 진흥 및 발전에 관한 사항
 2. 문화예술단체 지원 및 육성
@@ -11939,7 +12100,7 @@
 30. 공유림 및 백두대간 생태계 보전ㆍ관리</t>
       </text>
     </comment>
-    <comment ref="F286" authorId="0" shapeId="0">
+    <comment ref="F285" authorId="0" shapeId="0">
       <text>
         <t>1. 국소관 행정의 종합 기획조정
 2. 전통문화의 계승 발전
@@ -11970,7 +12131,7 @@
 27. 그 밖에 국내 다른 과에 속하지 아니하는 사항</t>
       </text>
     </comment>
-    <comment ref="G286" authorId="0" shapeId="0">
+    <comment ref="G285" authorId="0" shapeId="0">
       <text>
         <t>1. 관광정책 개발에 관한 사항
 2. 찻사발 축제 및 그 밖의 관광축제 업무
@@ -11990,7 +12151,7 @@
 16. 그 밖에 관광진흥 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="H286" authorId="0" shapeId="0">
+    <comment ref="H285" authorId="0" shapeId="0">
       <text>
         <t>1. 식품제조 및 즉석판매제조가공업
 2. 식품접객업(유흥·단란, 일반·휴게음식점, 제과점 등)
@@ -12016,7 +12177,7 @@
 22. 그 밖에 위생정책 행정에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="I286" authorId="0" shapeId="0">
+    <comment ref="I285" authorId="0" shapeId="0">
       <text>
         <t>1. 농정시책 기획·조정 및 평가에 관한 사항
 2. 농업·농촌 발전계획에 관한 사항
@@ -12045,7 +12206,7 @@
 25. 그 밖에 농업정책 사업 추진에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="J286" authorId="0" shapeId="0">
+    <comment ref="J285" authorId="0" shapeId="0">
       <text>
         <t>1. 농산물 유통구조개선 종합기획 조정
 2. 농산물 유통시설의 현대화 추진
@@ -12075,7 +12236,7 @@
 26. 그 밖에 농식품·축산물유통, 축산관련 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="K286" authorId="0" shapeId="0">
+    <comment ref="K285" authorId="0" shapeId="0">
       <text>
         <t>1. 포괄보조사업 총괄
 2. 귀농인 정착 지원사업
@@ -12123,7 +12284,7 @@
 44. 그 밖에 지역활력 및 도시재생 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="L286" authorId="0" shapeId="0">
+    <comment ref="L285" authorId="0" shapeId="0">
       <text>
         <t>1. 숲가꾸기
 2. 목재펠릿 보일러 보급 지원
@@ -12170,7 +12331,7 @@
 43. 그 밖에 산림녹지에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E287" authorId="0" shapeId="0">
+    <comment ref="E286" authorId="0" shapeId="0">
       <text>
         <t>1. 지역경제의 종합기획조정 및 육성지원
 2. 노정 및 근로자 복지증진
@@ -12221,7 +12382,7 @@
 47. 산지의 운영 및 관리</t>
       </text>
     </comment>
-    <comment ref="F287" authorId="0" shapeId="0">
+    <comment ref="F286" authorId="0" shapeId="0">
       <text>
         <t>1. 국소관 행정의 종합 기획조정
 2. 지역경제에 관한 종합 기획조정
@@ -12268,7 +12429,7 @@
 43. 그 밖에 국내 다른 과에 속하지 아니하는 사항</t>
       </text>
     </comment>
-    <comment ref="G287" authorId="0" shapeId="0">
+    <comment ref="G286" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보전종합계획 수립
 2. 환경성검토 및 환경영향평가 업무협의
@@ -12311,7 +12472,7 @@
 39. 그 밖에 환경보호 및 청소 관련 사항</t>
       </text>
     </comment>
-    <comment ref="H287" authorId="0" shapeId="0">
+    <comment ref="H286" authorId="0" shapeId="0">
       <text>
         <t>1. 교통행정의 종합기획
 2. 여객자동차 운수사업 관련 면허·인가·허가·등록
@@ -12343,7 +12504,7 @@
 28. 그 밖에 교통행정 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="I287" authorId="0" shapeId="0">
+    <comment ref="I286" authorId="0" shapeId="0">
       <text>
         <t>1. 전문건설업면허 등록·관리 및 행정처분
 2. 국토교통부 및 농림축산식품부 국유재산관리
@@ -12391,7 +12552,7 @@
 44. 그 밖에 건설행정 업무 및 건설 관련 공모사업에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="J287" authorId="0" shapeId="0">
+    <comment ref="J286" authorId="0" shapeId="0">
       <text>
         <t>1. 도시기본계획 수립에 관한 사항
 2. 도시관리계획 수립에 관한 사항
@@ -12426,7 +12587,7 @@
 31. 그 밖에 도시행정에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="K287" authorId="0" shapeId="0">
+    <comment ref="K286" authorId="0" shapeId="0">
       <text>
         <t>1. 재난안전본부운영 및 계획수립 등 재난 전반
 2. 시설물·건축물 안전점검 및 지도에 관한 사항
@@ -12477,7 +12638,7 @@
 47. 그 밖에 재난방재 및 하천 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="L287" authorId="0" shapeId="0">
+    <comment ref="L286" authorId="0" shapeId="0">
       <text>
         <t>1. 주택건설 종합계획의 수립·운영
 2. 국민주택기금 조성·운영
@@ -12526,7 +12687,7 @@
 45. 그 밖에 건축 및 경관업무에 관한 업무</t>
       </text>
     </comment>
-    <comment ref="M287" authorId="0" shapeId="0">
+    <comment ref="M286" authorId="0" shapeId="0">
       <text>
         <t>1. 개발행위허가 및 준공(토지형질변경, 토석채취, 물건적치)
 2. 개발행위분과위원회 운영
@@ -12557,7 +12718,7 @@
 27. 그 밖의 개발, 농지, 산림, 건축허가에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E288" authorId="0" shapeId="0">
+    <comment ref="E287" authorId="0" shapeId="0">
       <text>
         <t>1. 경제환경국 소관 행정사무의 종합기획 및 조정
 2. 일자리 창출 종합기획 및 조정
@@ -12576,7 +12737,7 @@
 15. 그 밖에 일자리경제, 교통행정, 산림, 공원녹지, 환경, 자원순환에 관한 사항 [제18호에서 이동 2022.12.30.]</t>
       </text>
     </comment>
-    <comment ref="F288" authorId="0" shapeId="0">
+    <comment ref="F287" authorId="0" shapeId="0">
       <text>
         <t>1. 국 소관 행정의 종합기획 및 조정
 2. 물가조사 및 가격표시제에 관한 사항
@@ -12593,7 +12754,7 @@
 13. 그 밖의 국내 다른 과에 속하지 아니하는 사항[제18조에서 이동 2022.12.30.]</t>
       </text>
     </comment>
-    <comment ref="G288" authorId="0" shapeId="0">
+    <comment ref="G287" authorId="0" shapeId="0">
       <text>
         <t>1. 교통 및 운수행정의 종합기획, 조정
 2. 자동차 운수사업의 지도·감독
@@ -12615,7 +12776,7 @@
 18. 그 밖의 교통행정에 관한 사항[제20조에서 이동 2022.12.30.]</t>
       </text>
     </comment>
-    <comment ref="H288" authorId="0" shapeId="0">
+    <comment ref="H287" authorId="0" shapeId="0">
       <text>
         <t>1. 산림행정의 종합기획 및 조정
 2. 양묘 및 조림 시행지도
@@ -12637,7 +12798,7 @@
 18. 그 밖의 산림에 관한 사항[제21조에서 이동 2022.12.30.]</t>
       </text>
     </comment>
-    <comment ref="I288" authorId="0" shapeId="0">
+    <comment ref="I287" authorId="0" shapeId="0">
       <text>
         <t>1. 공원행정의 종합기획 및 조정
 2. 도시공원·녹지 조성 및 보상
@@ -12654,7 +12815,7 @@
 13. 그 밖의 공원녹지에 관한 사항[제22조에서 이동 2022.12.30.]</t>
       </text>
     </comment>
-    <comment ref="J288" authorId="0" shapeId="0">
+    <comment ref="J287" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보전 종합계획 수립 및 시행
 2. 자연보호 운동의 추진
@@ -12680,7 +12841,7 @@
 22. 그 밖의 환경에 관한 사항[제23조에서 이동 2022.12.30.]</t>
       </text>
     </comment>
-    <comment ref="K288" authorId="0" shapeId="0">
+    <comment ref="K287" authorId="0" shapeId="0">
       <text>
         <t>1. 자원순환집행계획 수립
 2. 생활폐기물 수집ㆍ운반에 관한 사항
@@ -12696,7 +12857,7 @@
 12. 그 밖의 자원순환에 관한 사항[제24조에서 이동 2022.12.30.]</t>
       </text>
     </comment>
-    <comment ref="E289" authorId="0" shapeId="0">
+    <comment ref="E288" authorId="0" shapeId="0">
       <text>
         <t>1. 안전재난정책에 관한 사항  &lt;종전의 제17호에서 이동 2019.07.16., 종전의 제19호에서 이동 2020.09.14., 종전의 제20호에서 이동 2021.05.21., 종전의 제21호에서 이동 및 개정 2022.12.29., 종전의 제17호에서 이동 2023.12.31.&gt;
 2. 건설사업 지원에 관한 사항 &lt;종전의 제14호에서 이동 2019.07.16., 종전의 제16호에서 이동 2020.09.14., 종전의 제17호에서 이동 2021.05.21., 개정 2022.12.29., 종전의 제18호에서 이동 2023.12.31.&gt;3.도로사업 유지관리에 관한 사항 &lt;신설 2019.07.16., 종전의 제17호에서 이동 2020.09.14., 종전의 제18호에서 이동 2021.05.21., 개정 2022.12.29., 종전의 제19호에서 이동 2023.12.31.&gt;
@@ -12736,7 +12897,7 @@
 36. 상하수도사업소의 업무 지도·감독에 관한 사항  &lt;신설 2019.07.16., 종전의 제28호에서 이동 2020.09.14., 종전의 제29호에서 이동 2021.05.21., 종전의 제30호에서 이동 및 개정 2022.12.29., 종전의 제43호에서 이동 2023.12.31., 종전의 제33호에서 이동 2024.12.31.&gt;[제목개정 2019.07.16.][제목개정 2022.12.29.][제목개정 2024.12.31.]</t>
       </text>
     </comment>
-    <comment ref="F289" authorId="0" shapeId="0">
+    <comment ref="F288" authorId="0" shapeId="0">
       <text>
         <t>1. 안전재난재해 종합계획 수립 및 추진
 2. 재난관리 책임기관 및 긴급구조구난 기관협조 지원체계 구축
@@ -12754,7 +12915,7 @@
 14. 중대재해처벌법에 관한 사항  [종전의 제19조에서 이동 ]</t>
       </text>
     </comment>
-    <comment ref="G289" authorId="0" shapeId="0">
+    <comment ref="G288" authorId="0" shapeId="0">
       <text>
         <t>1. 일반농산어촌개발 신규사업 발굴, 예비계획수립, 신규사업 사업성 검토
 2. 창조적 마을 만들기 사업 시행 및 관리
@@ -12771,7 +12932,7 @@
 13. 주민자치에 관한 사항 [본조신설 2022.12.29.][종전의 제20조에서 이동 ]</t>
       </text>
     </comment>
-    <comment ref="H289" authorId="0" shapeId="0">
+    <comment ref="H288" authorId="0" shapeId="0">
       <text>
         <t>1. 신공항 이전 및 공동합의문 이행 추진에 관한 사항
 2. 신공항 관련 거버넌스 구성 및 운영(이전지원위원회, 행정협의체, 이전지원자문단 등)
@@ -12786,7 +12947,7 @@
 11. 드론 레포츠 활성화 [종전의 제21조에서 이동 ]</t>
       </text>
     </comment>
-    <comment ref="I289" authorId="0" shapeId="0">
+    <comment ref="I288" authorId="0" shapeId="0">
       <text>
         <t>1. 공동주택 관리
 2. 주거환경개선사업
@@ -12808,7 +12969,7 @@
 18. 공사금액 2,000만원 이상의 건설공사(설계용역ㆍ공사)  [종전의 제22조에서 이동 ][제목개정 2024.12.31.]</t>
       </text>
     </comment>
-    <comment ref="J289" authorId="0" shapeId="0">
+    <comment ref="J288" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보전 종합계획 수립
 2. 환경개선부담금 부과 징수 및 체납관리
@@ -12826,7 +12987,7 @@
 14. 가축위생ㆍ방역시설장비지원 [종전의 제21조에서 이동 및 제목개정 2022.12.29.][종전의 제23조에서 이동 ]</t>
       </text>
     </comment>
-    <comment ref="K289" authorId="0" shapeId="0">
+    <comment ref="K288" authorId="0" shapeId="0">
       <text>
         <t>1. 조림 계획수립 및 시행
 2. 숲가꾸기사업 계획 수립
@@ -12846,7 +13007,7 @@
 16. 국토공원화에 관한 업무  [종전의 제22조에서 이동 및 제목개정 2022.12.29.][종전의 제24조에서 이동 ]</t>
       </text>
     </comment>
-    <comment ref="E292" authorId="0" shapeId="0">
+    <comment ref="E291" authorId="0" shapeId="0">
       <text>
         <t>1. 농림관광국에 농업축산과, 유통지원과, 문화관광과, 산림녹지과를 둔다.
 2. 농림관광국의 분장사무는 다음 각 호와 같다.
@@ -12862,7 +13023,7 @@
 12. 녹지휴양시설 조성 및 관리에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="F292" authorId="0" shapeId="0">
+    <comment ref="F291" authorId="0" shapeId="0">
       <text>
         <t>1. 농정분야 총괄기획 조정
 2. 농가도우미지원 및 여성농업인 육성 사업
@@ -12921,7 +13082,7 @@
 55. 그 밖에 농업축산과 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="G292" authorId="0" shapeId="0">
+    <comment ref="G291" authorId="0" shapeId="0">
       <text>
         <t>1. 농산물 유통시설 및 유통기반 지원 확대
 2. 농산물 유통개선 종합계획
@@ -12953,7 +13114,7 @@
 28. 그 밖에 유통지원과 업무에 관한 사항 [종전 제5호부터 제25호가 제8호부터 제28호로 이동]</t>
       </text>
     </comment>
-    <comment ref="H292" authorId="0" shapeId="0">
+    <comment ref="H291" authorId="0" shapeId="0">
       <text>
         <t>1. 관광 및 영양군 이미지마케팅 총괄
 2. 지역축제업무 전반
@@ -12999,7 +13160,7 @@
 42. 그 밖에 문화관광과 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="I292" authorId="0" shapeId="0">
+    <comment ref="I291" authorId="0" shapeId="0">
       <text>
         <t>1. 조림 및 숲가꾸기 사업
 2. 산림경영계획인가 및 사업신고 수리 업무
@@ -13035,7 +13196,7 @@
 32. 그 밖에 산림녹지과 업무에 관한 사항 [종전 제8호부터 제32호가 제10호부터 제34호로 이동]</t>
       </text>
     </comment>
-    <comment ref="E293" authorId="0" shapeId="0">
+    <comment ref="E292" authorId="0" shapeId="0">
       <text>
         <t>1. 경제건설국에 농촌경제과, 건설안전과, 지역개발과, 환경보전과, 양수발전건립추진단을 둔
 2. 경제건설국의 분장사무는 다음 각 호와 같
@@ -13056,7 +13217,7 @@
 17. 발전소 주변지역 종합개발계획 수립 및 시행에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="F293" authorId="0" shapeId="0">
+    <comment ref="F292" authorId="0" shapeId="0">
       <text>
         <t>1. 지역경제 및 경제동향 분석
 2. 상공 및 시장관리업무
@@ -13086,7 +13247,7 @@
 26. 그 밖에 농촌경제과 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="G293" authorId="0" shapeId="0">
+    <comment ref="G292" authorId="0" shapeId="0">
       <text>
         <t>1. 국가기반보호 업무에 관한 사항
 2. 국도 및 지방도 공공사업 편입용지 보상 업무
@@ -13150,7 +13311,7 @@
 60. 그 밖에 건설안전과 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="H293" authorId="0" shapeId="0">
+    <comment ref="H292" authorId="0" shapeId="0">
       <text>
         <t>1. 소규모주민숙원사업
 2. 농촌생활환경 정비사업
@@ -13179,7 +13340,7 @@
 25. 그 밖에 지역개발과 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="I293" authorId="0" shapeId="0">
+    <comment ref="I292" authorId="0" shapeId="0">
       <text>
         <t>1. 그린영양21 추진
 2. 자연환경보전 및 행락질서 업무
@@ -13230,7 +13391,7 @@
 47. 그 밖에 환경보전과 업무에 관한 사항 [종전 제12호부터 제38호가 제20호부터 제46호로 이동]</t>
       </text>
     </comment>
-    <comment ref="J293" authorId="0" shapeId="0">
+    <comment ref="J292" authorId="0" shapeId="0">
       <text>
         <t>1. 양수발전소 건설 관련 행정 절차 지원
 2. 양수발전소 건립지역 주민 및 관계 기관과의 소통 및 협조
@@ -13248,7 +13409,7 @@
 14. 기타 양수발전소 건립추진 업무에 관한 사항[본조신설 2025.12.19.]</t>
       </text>
     </comment>
-    <comment ref="E294" authorId="0" shapeId="0">
+    <comment ref="E293" authorId="0" shapeId="0">
       <text>
         <t>1. 생태공원 관리 행정의 종합 및 기획
 2. 반딧불이 생태계 조사ㆍ연구ㆍ보호관리ㆍ사육
@@ -13257,7 +13418,7 @@
 5. 그 밖에 생태공원사업소의 운영에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E297" authorId="0" shapeId="0">
+    <comment ref="E296" authorId="0" shapeId="0">
       <text>
         <t>1. 관광업무의 종합계획 및 조정에 관한 사항
 2. 관광개발 및 홍보에 관한 사항
@@ -13294,7 +13455,36 @@
 33. 물관리사업소의 업무 지도ㆍ감독에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E302" authorId="0" shapeId="0">
+    <comment ref="E297" authorId="0" shapeId="0">
+      <text>
+        <t>1. 환경보전 종합계획 수립
+2. 자연환경보전이용시설 설치 및 관리
+3. 미세먼지 대응 관련 업무
+4. 오염총량관리제 시행 관련 업무
+5. 수질오염 사고 대책 추진
+6. 폐기물처리업 허가, 신고 및 관리
+7. 상수도시설의 설치 및 유지관리
+8. 상수원 보호구역 관리
+9. 하수처리시설 설치사업 추진 및 운영
+10. 가축분뇨 공공처리시설 관리ㆍ운영</t>
+      </text>
+    </comment>
+    <comment ref="E298" authorId="0" shapeId="0">
+      <text>
+        <t>1. 산림경영 계획 인가 및 신고
+2. 산림재해예방사업 및 사방사업
+3. 농림사업(임업분야)
+4. 산림보호구역 관리
+5. 산림병해충 예찰 및 방제(예찰방제단 운용)
+6. 소나무재선충병 예찰ㆍ방제
+7. 산불방지종합대책 수립 (예방 및 진화)
+8. 도시숲 기본계획 수립 및 조성ㆍ관리
+9. 조경지 유지관리
+10. 보호수 지정ㆍ해제 및 관리
+11. 가로수 조성 및 관리</t>
+      </text>
+    </comment>
+    <comment ref="E301" authorId="0" shapeId="0">
       <text>
         <t>1. 국토건설종합계획의 수립 및 시행
 2. 국유재산(도로)의 관리 및 용도폐지
@@ -13327,7 +13517,7 @@
 29. 그 밖에 건설, 안전관리, 도시계획, 건축디자인, 환경관리, 산림녹지에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="F302" authorId="0" shapeId="0">
+    <comment ref="F301" authorId="0" shapeId="0">
       <text>
         <t>1. 국유재산(도로)의 관리 및 용도폐지
 2. 지하수 관리에 관한 업무
@@ -13341,7 +13531,7 @@
 10. 하천시설물의 정비ㆍ관리에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="G302" authorId="0" shapeId="0">
+    <comment ref="G301" authorId="0" shapeId="0">
       <text>
         <t>1. 사회재난 정책 총괄·조정
 2. 안전관리 및 안전문화 업무
@@ -13352,7 +13542,7 @@
 7. 중대재해예방 총괄 및 관리 업무</t>
       </text>
     </comment>
-    <comment ref="H302" authorId="0" shapeId="0">
+    <comment ref="H301" authorId="0" shapeId="0">
       <text>
         <t>1. 군기본계획 수립 및 군관리계획 결정
 2. 개발행위 허가 및 관리
@@ -13365,7 +13555,7 @@
 9. 산업단지 조성 추진 [전문개정 2022.12.30.]</t>
       </text>
     </comment>
-    <comment ref="I302" authorId="0" shapeId="0">
+    <comment ref="I301" authorId="0" shapeId="0">
       <text>
         <t>1. 건축행정 전산화 운영
 2. 건축물 관리대장 및 발급
@@ -13382,7 +13572,7 @@
 13. 대체산림조성비 및 복구비 부과·체납관리</t>
       </text>
     </comment>
-    <comment ref="J302" authorId="0" shapeId="0">
+    <comment ref="J301" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보전 종합계획 수립
 2. 환경개선부담금 부과 및 징수
@@ -13403,7 +13593,7 @@
 17. 재활용품 및 영농폐비닐 수거·처리</t>
       </text>
     </comment>
-    <comment ref="K302" authorId="0" shapeId="0">
+    <comment ref="K301" authorId="0" shapeId="0">
       <text>
         <t>1. 산림계획 및 조림에 관한 업무
 2. 산지전용 허가 및 토석채취 허가
@@ -13417,7 +13607,7 @@
 10. 공원 및 녹지관리 전반</t>
       </text>
     </comment>
-    <comment ref="E303" authorId="0" shapeId="0">
+    <comment ref="E302" authorId="0" shapeId="0">
       <text>
         <t>1. 지역경제 및 시장에 관한 사항
 2. 일자리 창출, 사회적 기업 육성 등에 관한 사항
@@ -13444,7 +13634,7 @@
 23. 농업생산기반시설 정비에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="F303" authorId="0" shapeId="0">
+    <comment ref="F302" authorId="0" shapeId="0">
       <text>
         <t>1. 지역경제에 관한 종합 기획ㆍ조정 및 활성화 추진
 2. 새마을단체 육성ㆍ관리
@@ -13464,7 +13654,7 @@
 16. 농촌가로등 관리</t>
       </text>
     </comment>
-    <comment ref="G303" authorId="0" shapeId="0">
+    <comment ref="G302" authorId="0" shapeId="0">
       <text>
         <t>1. 농업행정의 종합ㆍ기획ㆍ조정에 관한 사항
 2. 농촌 소득원 개발사업
@@ -13494,7 +13684,7 @@
 26. 디지털 혁신 농업 타운 업무</t>
       </text>
     </comment>
-    <comment ref="H303" authorId="0" shapeId="0">
+    <comment ref="H302" authorId="0" shapeId="0">
       <text>
         <t>1. 산림계획 및 조림에 관한 업무
 2. 산림경영계획 인가
@@ -13518,7 +13708,7 @@
 20. 산촌생태마을 관리</t>
       </text>
     </comment>
-    <comment ref="I303" authorId="0" shapeId="0">
+    <comment ref="I302" authorId="0" shapeId="0">
       <text>
         <t>1. 축산업 경쟁력 제고 및 축산기반 조성
 2. 축산업 등록제 관리
@@ -13539,7 +13729,7 @@
 17. 공수의사 및 공중방역수의사 관리</t>
       </text>
     </comment>
-    <comment ref="J303" authorId="0" shapeId="0">
+    <comment ref="J302" authorId="0" shapeId="0">
       <text>
         <t>1. 농촌협약, 농촌뉴딜사업
 2. 일반농산어촌개발사업(농촌중심지, 기초생활거점육성, 마을만들기)
@@ -13555,7 +13745,7 @@
 12. 농촌주택개량사업 및 농촌빈집정비사업</t>
       </text>
     </comment>
-    <comment ref="E304" authorId="0" shapeId="0">
+    <comment ref="E303" authorId="0" shapeId="0">
       <text>
         <t>1. 군 건설 종합계획의 수립·추진에 관한 사항
 2. 국유재산(도로), 접도구역 관리에 관한 사항
@@ -13585,7 +13775,7 @@
 26. 청소행정에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="F304" authorId="0" shapeId="0">
+    <comment ref="F303" authorId="0" shapeId="0">
       <text>
         <t>1. 군 건설 종합계획 수립 추진
 2. 국유재산(도로) 관리, 접도구역 및 도로부지 관리
@@ -13611,7 +13801,7 @@
 22. 불법주정차, 무단방치 차량 지도 단속</t>
       </text>
     </comment>
-    <comment ref="G304" authorId="0" shapeId="0">
+    <comment ref="G303" authorId="0" shapeId="0">
       <text>
         <t>1. 안전재난정책 총괄ㆍ조정
 2. 사회적 재난 대응 총괄
@@ -13635,7 +13825,7 @@
 20. 영상기기(CCTV) 설치 및 유지관리</t>
       </text>
     </comment>
-    <comment ref="H304" authorId="0" shapeId="0">
+    <comment ref="H303" authorId="0" shapeId="0">
       <text>
         <t>1. 도시관리종합계획 수립 및 실시
 2. 군계획의 입안 및 정비
@@ -13658,7 +13848,7 @@
 19. 예천온천장 관리 운영</t>
       </text>
     </comment>
-    <comment ref="I304" authorId="0" shapeId="0">
+    <comment ref="I303" authorId="0" shapeId="0">
       <text>
         <t>1. 위반건축물 지도 및 단속
 2. 건축물대장 관리 및 등기촉탁 업무
@@ -13674,7 +13864,7 @@
 12. 청사 건립(증축, 개축, 대수선, 리모델링 포함)</t>
       </text>
     </comment>
-    <comment ref="J304" authorId="0" shapeId="0">
+    <comment ref="J303" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보전 종합계획 수립
 2. 대기, 소음, 진동, 토양 분야 업무(배출시설 포함)
@@ -13699,7 +13889,7 @@
 21. 환경미화원 및 청소차량 통합 관리 운영</t>
       </text>
     </comment>
-    <comment ref="E307" authorId="0" shapeId="0">
+    <comment ref="E306" authorId="0" shapeId="0">
       <text>
         <t>1. 안전기획, 안전문화, 각종 재난 대응지원 및 방재, 재난복구에 관한 사항
 2. 국가 기반보호, 민방위 비상대비 등에 관한 사항
@@ -13711,7 +13901,7 @@
 8. 하천 및 도로 관리 및 토목에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="F307" authorId="0" shapeId="0">
+    <comment ref="F306" authorId="0" shapeId="0">
       <text>
         <t>1. 안전재난정책 총괄ㆍ조정
 2. 인적ㆍ사회적재난 대응 총괄
@@ -13731,7 +13921,7 @@
 16. 지역 산업재해 예방 활동 업무 [본조신설 2018.3.27.]</t>
       </text>
     </comment>
-    <comment ref="G307" authorId="0" shapeId="0">
+    <comment ref="G306" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보전 종합계획 수립 조정
 2. 환경영향 평가에 관한 사항
@@ -13762,7 +13952,7 @@
 27. 자연보호에 관한 업무</t>
       </text>
     </comment>
-    <comment ref="H307" authorId="0" shapeId="0">
+    <comment ref="H306" authorId="0" shapeId="0">
       <text>
         <t>1. 산림경영 계획
 2. 양묘 및 조림사업 시행 지도
@@ -13785,7 +13975,7 @@
 19. 정원조성에 관한 사항[제목개정 2022.10.11.]</t>
       </text>
     </comment>
-    <comment ref="I307" authorId="0" shapeId="0">
+    <comment ref="I306" authorId="0" shapeId="0">
       <text>
         <t>1. 도시계획의 입안 및 결정
 2. 도시계획구역 내 토지수용 및 용지매수 보상
@@ -13810,7 +14000,7 @@
 21. 삭제 [제목개정 2017.5.1.][제목개정 2018.8.23.]</t>
       </text>
     </comment>
-    <comment ref="J307" authorId="0" shapeId="0">
+    <comment ref="J306" authorId="0" shapeId="0">
       <text>
         <t>1. 건설관리
 2. 건설기계 및 조종사 관리
@@ -13829,7 +14019,16 @@
 15. 마을회관 신·개축사업 및 유지관리</t>
       </text>
     </comment>
-    <comment ref="E310" authorId="0" shapeId="0">
+    <comment ref="E307" authorId="0" shapeId="0">
+      <text>
+        <t>1. 관광 기획, 관광객 수용대책 및 관광홍보에 관한 사항
+2. 관광지구·시설 개발에 관한 사항
+3. 산림관광 계획 수립 및 추진에 관한 사항
+4. 산림보존 계획 수립 및 추진에 관한 사항
+5. 꽃섬추진에 관한 사항[본조신설 2024. 7. 8.]</t>
+      </text>
+    </comment>
+    <comment ref="E309" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보전 종합계획 수립추진에 관한 사항
 2. 자연생태, 야생동물 구조ㆍ관리, 기후변화대응에 관한 사항
@@ -13841,7 +14040,7 @@
 8. 그 밖에 기후환경 정책에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E311" authorId="0" shapeId="0">
+    <comment ref="E310" authorId="0" shapeId="0">
       <text>
         <t>1. 산림기본계획 수립ㆍ시행 및 산림자원 조성ㆍ관리에 관한 사항
 2. 산림문화휴양시설 및 산림관광기반시설 조성과 관리에 관한 사항
@@ -13849,7 +14048,7 @@
 4. 그 밖에 산림에 관한 사항[본조신설 2024.06.27.]</t>
       </text>
     </comment>
-    <comment ref="E312" authorId="0" shapeId="0">
+    <comment ref="E311" authorId="0" shapeId="0">
       <text>
         <t>1. 환경정책 총괄, 환경교육, 수질보전, 자전거 이용 활성화에 관한 사항
 2. 탄소중립정책, 기후위기 대응, 대기ㆍ미세먼지에 관한 사항
@@ -13857,7 +14056,7 @@
 4. 하천정비계획 수립ㆍ시행, 생태하천 복원 및 자연형 하천 정비, 소하천, 국가하천 관리에 관한 사항[본조신설</t>
       </text>
     </comment>
-    <comment ref="F312" authorId="0" shapeId="0">
+    <comment ref="F311" authorId="0" shapeId="0">
       <text>
         <t>1. 환경정책 종합계획 수립 및 시행에 관한 사항
 2. 환경교육 기본계획 수립 및 추진에 관한 사항
@@ -13866,7 +14065,7 @@
 5. 삭제 [제36조에서 이동]</t>
       </text>
     </comment>
-    <comment ref="G312" authorId="0" shapeId="0">
+    <comment ref="G311" authorId="0" shapeId="0">
       <text>
         <t>1. 탄소중립도시 총괄계획 수립 및 추진에 관한 사항
 2. 기후위기 대응에 관한 사항
@@ -13874,7 +14073,7 @@
 4. 미세먼지 관리 총괄계획 수립 및 추진에 관한 사항[본조신설 2023.1.2.]</t>
       </text>
     </comment>
-    <comment ref="H312" authorId="0" shapeId="0">
+    <comment ref="H311" authorId="0" shapeId="0">
       <text>
         <t>1. 생활폐기물 처리에 관한 기본계획 수립 및 추진에 관한 사항
 2. 생활폐기물 수집ㆍ운반 및 청소대행업체 관리에 관한 사항
@@ -13884,7 +14083,7 @@
 6. 소각시설 및 재활용처리시설 설치ㆍ운영ㆍ지도에 관한 사항[종전 제37조에서 이동 ]</t>
       </text>
     </comment>
-    <comment ref="I312" authorId="0" shapeId="0">
+    <comment ref="I311" authorId="0" shapeId="0">
       <text>
         <t>1. 하천 정비계획 수립 및 시행에 관한 사항
 2. 생태하천 복원 및 자연형 하천정비 등에 관한 사항
@@ -13893,7 +14092,7 @@
 5. 낙동강, 창원천 등 국가하천 유지관리 전반에 관한 사항[종전 제52조에서 이동 ]</t>
       </text>
     </comment>
-    <comment ref="E313" authorId="0" shapeId="0">
+    <comment ref="E312" authorId="0" shapeId="0">
       <text>
         <t>1. 환경정책 수립 및 환경보전에 관한 사항
 2. 수질오염총량제 및 수변구역관리에 관한 사항
@@ -13903,7 +14102,7 @@
 6. 공원녹지 조성 및 관리에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E314" authorId="0" shapeId="0">
+    <comment ref="E313" authorId="0" shapeId="0">
       <text>
         <t>1. 20.)
 2. 수산행정, 어업지도, 어선관리, 수산식품개발에 관한 사항
@@ -13914,7 +14113,7 @@
 7. 20.]</t>
       </text>
     </comment>
-    <comment ref="F314" authorId="0" shapeId="0">
+    <comment ref="F313" authorId="0" shapeId="0">
       <text>
         <t>1. 수산진흥의 종합기획 및 조정
 2. 수산단체 및 어민 기술지도ㆍ관리
@@ -13927,7 +14126,7 @@
 9. 국제규제 관련 어업인 지원 사업 [제27조에서 이동(2019.12.20.), 제31조에서 이동, 종전 제32조는 제33조로 이동] [제32조에서 이동, 종전 제31조는 제30조로 이동(2022.12.26.)] [제31조에서 이동, 종전 제32조는 제33조로 이동 ] [제32조에서 이동, 종전 제34조는 제36조로 이동 ]</t>
       </text>
     </comment>
-    <comment ref="G314" authorId="0" shapeId="0">
+    <comment ref="G313" authorId="0" shapeId="0">
       <text>
         <t>1. 마을어장 자원조성사업
 2. 양식 어업권 관리
@@ -13940,7 +14139,7 @@
 9. 삭제  [제28조에서 이동(2019.12.20.), 제32조에서 이동, 종전 제33조는 제34조로 이동] [제33조에서 이동, 종전 제32조는 제31조로 이동(2022.12.26.)] [제32조에서 이동 ] [제33조에서 이동, 종전 제35조는 제20조로 이동 ]</t>
       </text>
     </comment>
-    <comment ref="H314" authorId="0" shapeId="0">
+    <comment ref="H313" authorId="0" shapeId="0">
       <text>
         <t>1. 공유수면매립 기본 계획 수립 및 점사용 허가 업무
 2. 해상운송업무에 관한 사항
@@ -13950,7 +14149,7 @@
 6. 깨끗한 바다 가꾸기 사업 [제34조에서 이동, 종전 제36조는 제37조로 이동 ]</t>
       </text>
     </comment>
-    <comment ref="I314" authorId="0" shapeId="0">
+    <comment ref="I313" authorId="0" shapeId="0">
       <text>
         <t>1. 자연보호에 관한 종합계획 수립 및 국토대청결 운동 추진
 2. 환경영향평가 및 환경개선부담금에 관한 사항
@@ -13962,7 +14161,7 @@
 8. 위생환경시설 지도 감독 [제20조에서 이동(2019.12.20.), 제34조에서 이동, 종전 제35조는 제36조로 이동] [제35조에서 이동, 종전 제36조는 제37조로 이동 ] [제36조에서 이동, 종전 제36조는 제38조로 이동 ]</t>
       </text>
     </comment>
-    <comment ref="J314" authorId="0" shapeId="0">
+    <comment ref="J313" authorId="0" shapeId="0">
       <text>
         <t>1. 생활폐기물 자원화계획 수립 및 사업 추진
 2. 쓰레기 감량과 재활용에 관한 사항
@@ -13971,7 +14170,7 @@
 5. 폐기물 처리에 관한 사항 [제35조에서 이동, 종전 제36조는 제30조로 이동] [제36조에서 이동, 종전 제37조는 제38조로 이동 ] [제37조에서 이동, 종전 제38조는 제39조로 이동 ]</t>
       </text>
     </comment>
-    <comment ref="E315" authorId="0" shapeId="0">
+    <comment ref="E314" authorId="0" shapeId="0">
       <text>
         <t>1. 주민생활지원서비스 종합계획 수립ㆍ조정에 관한 사항
 2. 서비스연계 및 복지대상자 통합조사에 관한 사항
@@ -13980,7 +14179,7 @@
 5. 환경보전에 관한 사항[본조신설 2024.7.15.]</t>
       </text>
     </comment>
-    <comment ref="E316" authorId="0" shapeId="0">
+    <comment ref="E315" authorId="0" shapeId="0">
       <text>
         <t>1. 환경국에 환경정책과, 기후대응과, 자원순환과, 하천과를 둔다.
 2. 환경국장은 다음 업무를 분담한다.
@@ -13990,7 +14189,7 @@
 6. 수자원정책, 하천, 지하수에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E317" authorId="0" shapeId="0">
+    <comment ref="E316" authorId="0" shapeId="0">
       <text>
         <t>1. 국 소관 행정의 종합 조정
 2. 지역경제, 소상공인, 일자리지원, 에너지관리에 관한 사항
@@ -14001,7 +14200,7 @@
 7. 산림행정, 산림경영, 산림보호병해충, 산림휴양림, 공원관리, 가로수관리에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="F317" authorId="0" shapeId="0">
+    <comment ref="F316" authorId="0" shapeId="0">
       <text>
         <t>1. 국ㆍ과 소관 행정 종합조정
 2. 지역경제 활성화 대책 추진
@@ -14031,7 +14230,7 @@
 26. 그 밖의 지역경제, 소상공인, 일자리지원, 에너지관리 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="G317" authorId="0" shapeId="0">
+    <comment ref="G316" authorId="0" shapeId="0">
       <text>
         <t>1. 나노융합산업 육성 및 기획 조정
 2. 나노융합산업전 및 세미나 추진
@@ -14045,7 +14244,7 @@
 10. 그 밖의 나노융합, 국가산단지원, 연구개발지원 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="H317" authorId="0" shapeId="0">
+    <comment ref="H316" authorId="0" shapeId="0">
       <text>
         <t>1. 투자유치사업 종합개발계획 수립 및 조정
 2. 기업유치 기획 조정
@@ -14061,7 +14260,7 @@
 12. 그 밖의 투자유치, 기업지원, 산업단지, 물류클러스터 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="I317" authorId="0" shapeId="0">
+    <comment ref="I316" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보전 종합계획수립 조정
 2. 청소행정의 종합 조정
@@ -14086,7 +14285,7 @@
 21. 그 밖의 환경정책, 기후대응, 생활환경, 수계관리, 청소행정, 환경시설, 폐기물관리 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="J317" authorId="0" shapeId="0">
+    <comment ref="J316" authorId="0" shapeId="0">
       <text>
         <t>1. 교통행정의 종합기획 조정
 2. 자동차 운수사업의 지도 감독
@@ -14102,7 +14301,7 @@
 12. 그 밖의 교통행정, 교통시설지도, 교통관리, 차량등록 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="K317" authorId="0" shapeId="0">
+    <comment ref="K316" authorId="0" shapeId="0">
       <text>
         <t>1. 산림행정의 종합계획 수립
 2. 양묘 및 조림사업 시행지도
@@ -14137,7 +14336,7 @@
 31. 그 밖의 산림행정, 산림경영, 산림보호병해충, 산림휴양림, 공원관리, 가로수관리 업무에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E318" authorId="0" shapeId="0">
+    <comment ref="E317" authorId="0" shapeId="0">
       <text>
         <t>1. 환경녹지국에 자원순환과, 기후환경과, 상하수도과, 산림과, 공원과를 둔
 2. 환경녹지국장은 다음 사항을 나눠 맡는
@@ -14158,7 +14357,7 @@
 17. 도시녹화, 공원관리에 관한 사항[본조신설 2024.11.21.]</t>
       </text>
     </comment>
-    <comment ref="F318" authorId="0" shapeId="0">
+    <comment ref="F317" authorId="0" shapeId="0">
       <text>
         <t>1. 자원순환과장은 지방행정사무관 또는 지방환경사무관으로 한다.
 2. 자원순환과장은 다음 사항을 나눠 맡는다.
@@ -14170,7 +14369,7 @@
 8. 국(局)내에 다른 과에 속하지 않는 사항</t>
       </text>
     </comment>
-    <comment ref="G318" authorId="0" shapeId="0">
+    <comment ref="G317" authorId="0" shapeId="0">
       <text>
         <t>1. 기후환경과장은 지방행정사무관 또는 지방환경사무관으로 한다.
 2. 기후환경과장은 다음 사항을 나눠 맡는
@@ -14183,7 +14382,7 @@
 9. 공중화장실 관리에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="H318" authorId="0" shapeId="0">
+    <comment ref="H317" authorId="0" shapeId="0">
       <text>
         <t>1. 상하수도과장은 지방행정사무관 또는 지방시설사무관으로 한다.
 2. 상하수도과장은 다음 사항을 나눠 맡는다.
@@ -14194,7 +14393,7 @@
 7. 하수도 관리에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="I318" authorId="0" shapeId="0">
+    <comment ref="I317" authorId="0" shapeId="0">
       <text>
         <t>1. 산림과장은 지방농업사무관 또는 지방녹지사무관으로 한다.
 2. 산림과장은 다음 사항을 나눠 맡는
@@ -14204,7 +14403,7 @@
 6. 임도, 등산로, 섬앤섬길, 남파랑길 등 기반시설 조성 및 관리에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="J318" authorId="0" shapeId="0">
+    <comment ref="J317" authorId="0" shapeId="0">
       <text>
         <t>1. 공원과장은 지방행정사무관 또는 지방농업사무관 또는 지방녹지사무관 또는 지방시설사무관으로 한
 2. 공원과장은 다음 사항을 나눠 맡는
@@ -14216,7 +14415,7 @@
 8. 삭제 [종전 제43조는 제44조로 이동 ][제58조에서 이동 ]</t>
       </text>
     </comment>
-    <comment ref="E319" authorId="0" shapeId="0">
+    <comment ref="E318" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보전, 대기환경, 기후변화 대응에 관한 사항
 2. 수질오염 및 비점오염 저감, 환경오염 지도ㆍ점검 관리에 관한 사항
@@ -14226,7 +14425,7 @@
 6. 도시공간 녹화, 도시공원 및 자연공원 관리에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E320" authorId="0" shapeId="0">
+    <comment ref="E319" authorId="0" shapeId="0">
       <text>
         <t>1. 경제문화국에 경제기업과, 문화관광과, 환경과, 산림휴양과를 둔다.
 2. 경제문화국의 분장사무는 다음 각 호와 같다.
@@ -14236,12 +14435,15 @@
 6. 산림종합개발계획, 산림자원, 산림보호, 산림휴양시설에 관한 사항</t>
       </text>
     </comment>
+    <comment ref="E320" authorId="0" shapeId="0">
+      <text>
+        <t>1. 친환경골프장 운영에 관한 종합계획 수립, 시행
+2. 친환경골프장, 클럽하우스 등 시설물 관리
+3. 친환경골프장 특별회계 관리 운영
+4. 골프코스, 잔디 및 그 밖에 부대되는 시설관리 및 운영</t>
+      </text>
+    </comment>
     <comment ref="E321" authorId="0" shapeId="0">
-      <text>
-        <t>읍ㆍ면은 행정의 능률과 주민편의를 도모하기 위하여 가족관계등록ㆍ주민등록업무, 민원서류발급, 이·반조직 운영, 주민자치센터 운영 등 지방행정의 기초사무를 관장한다.</t>
-      </text>
-    </comment>
-    <comment ref="E322" authorId="0" shapeId="0">
       <text>
         <t>1. 복지환경국에 복지정책과, 주민복지과, 환경과, 산림녹지과를 둔
 2. 복지환경국의 분장사무는 다음 각 호와 같다.
@@ -14251,7 +14453,7 @@
 6. 산림, 녹지에 관한 사항[신설</t>
       </text>
     </comment>
-    <comment ref="E323" authorId="0" shapeId="0">
+    <comment ref="E322" authorId="0" shapeId="0">
       <text>
         <t>1. 관광정책, 관광마케팅, 체육지원, 스포츠마케팅, 관광체육시설, 온천에 관한 사항
 2. 문화예술, 문화유산, 문화시설, 박물관, 문화예술회관, 도서관에 관한 사항
@@ -14260,7 +14462,7 @@
 5. 생태정책, 생태관, 따오기관리, 따오기서식, 따오기보존, 우포유스호스텔에 관한 사항[본조신설 2019.11.27.]</t>
       </text>
     </comment>
-    <comment ref="E324" authorId="0" shapeId="0">
+    <comment ref="E323" authorId="0" shapeId="0">
       <text>
         <t>1. 문화예술 및 문화시설·산업, 문화유산관리, 문화유산정책, 박물관 운영 등에 관한 사항
 2. 관광정책, 생태관광, 관광개발 및 관광기반조성, 해양관광, 당항포관광지 등에 관한 관리·운영 사항
@@ -14271,7 +14473,7 @@
 7. 조 2529]</t>
       </text>
     </comment>
-    <comment ref="E325" authorId="0" shapeId="0">
+    <comment ref="E324" authorId="0" shapeId="0">
       <text>
         <t>1. 해양정책, 어항관리, 해양보전, 해양레저에 관한 사항
 2. 수산진흥, 수산식품, 수산양식, 자원조성, 어업지원에 관한 사항
@@ -14281,7 +14483,7 @@
 6. 산림조성, 산림보호, 산림휴양, 공원녹지에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E326" authorId="0" shapeId="0">
+    <comment ref="E325" authorId="0" shapeId="0">
       <text>
         <t>1. 문화예술, 국가유산, 체육정책, 체육기반, 체육시설 등 문화체육에에 관한 사항
 2. 관광기획, 관광개발, 관광마케팅, 관광시설 등 관광진흥에 관한 사항
@@ -14290,12 +14492,12 @@
 5. 상수도운영, 상수도시설, 하수도시설, 하수도운영 등 수도사업에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E327" authorId="0" shapeId="0">
+    <comment ref="E326" authorId="0" shapeId="0">
       <text>
         <t>항노화관광국에한방항노화과·문화체육과·관광진흥과·산림녹지과·환경위생과를 둔다.[종전 제3조의3는 제3조의4으로 이동 &lt;2023.12.28.&gt; [본조신설 2019.12.26.] [제3조의2에서 이동 &lt;2023.12.38.&gt;]</t>
       </text>
     </comment>
-    <comment ref="F327" authorId="0" shapeId="0">
+    <comment ref="F326" authorId="0" shapeId="0">
       <text>
         <t>1. 항노화산업 육성에 관한 사항
 2. 한방항노화제약산업단지 기업유치에 관한 사항
@@ -14318,7 +14520,7 @@
 19. 그 밖의 한방항노화 업무에 관한 사항 [제6조에서 이동, 종전 제11조는 제7조로 이동 ] [제목개정 2019.12.26.] [제11조에서 이동, 종전 제12조는 제13조로 이동 ]</t>
       </text>
     </comment>
-    <comment ref="G327" authorId="0" shapeId="0">
+    <comment ref="G326" authorId="0" shapeId="0">
       <text>
         <t>1. 문화체육 종합계획의 수립
 2. 문화예술행사 기획추진
@@ -14333,7 +14535,7 @@
 11. 그 밖의 문화·체육 업무에 관한 사항 [제11조에서 이동, 종전 제12조는 제13조로 이동 ] [제12조에서 이동, 종전 제13조는 제14조로 이동 ]</t>
       </text>
     </comment>
-    <comment ref="H327" authorId="0" shapeId="0">
+    <comment ref="H326" authorId="0" shapeId="0">
       <text>
         <t>1. 관광종합개발계획 수립에 관한 사항
 2. 관광마케팅에 관한 사항
@@ -14344,7 +14546,7 @@
 7. 그 밖의 관광진흥업무에 관한 사항 [제12조에서 이동, 종전 제13조는 제14조로 이동 ] [제13조에서 이동, 종전 제14조는 제15조로 이동 ]</t>
       </text>
     </comment>
-    <comment ref="I327" authorId="0" shapeId="0">
+    <comment ref="I326" authorId="0" shapeId="0">
       <text>
         <t>1. 조림, 육림, 양모사업
 2. 광물(고령토 등)채취 허가, 토석채취 허가·신고
@@ -14365,7 +14567,7 @@
 17. 그 밖의 산림업무에 관한 사항 [제13조에서 이동, 종전 제14조는 제9조로 이동 ] [제14조에서 이동, 종전 제15조는 제16조로 이동 ]</t>
       </text>
     </comment>
-    <comment ref="J327" authorId="0" shapeId="0">
+    <comment ref="J326" authorId="0" shapeId="0">
       <text>
         <t>1. 환경보전종합계획 수립지도
 2. 환경영향 평가서 초안 공람 및 주민의견 수렴
@@ -14384,7 +14586,7 @@
 15. 그 밖의 환경 및 위생업무에 관한 사항 [제14조에서 이동, 종전 제9조는 제11조로 이동 ] [제9조에서 이동, 종전 제18조는 제19조로 이동 ] [제18조에서 이동, 종전 제19조는 제20조로 이동 ] [제91조에서 이동 ] [종전 제16조는 제9조로 이동 ]</t>
       </text>
     </comment>
-    <comment ref="E328" authorId="0" shapeId="0">
+    <comment ref="E327" authorId="0" shapeId="0">
       <text>
         <t>1. 경제, 일자리창출, 기업지원, 에너지, 기업유치
 2. 인구정책, 교류협력, 지역활력, 귀농귀촌
@@ -14393,7 +14595,7 @@
 5. 환경정책, 환경관리, 자원순환, 환경시설, 환경보건</t>
       </text>
     </comment>
-    <comment ref="E329" authorId="0" shapeId="0">
+    <comment ref="E328" authorId="0" shapeId="0">
       <text>
         <t>1. 안전기획, 재난상황, 복구지원, 중대재해, 민방위
 2. 건설행정, 도로, 하천, 농업기반, 교통
@@ -14402,7 +14604,7 @@
 5. 산삼, 항노화, 산삼마케팅, 휴양관리, 휴양시설</t>
       </text>
     </comment>
-    <comment ref="E330" authorId="0" shapeId="0">
+    <comment ref="E329" authorId="0" shapeId="0">
       <text>
         <t>1. 재난안전관리정책, 재난대응총괄, 자연재난, 안전점검, 중대재해예방, 민방위, 통신· CCTV 관제, 재난안전상황실 운영 등 안전에 관한 사항(2024.12.31.)
 2. 산림조성, 산림소득, 화강석 육성, 산림보호, 공원·녹지 조성관리, 산림레포츠, 힐링랜드 운영 등 산림에 관한 사항
@@ -14411,7 +14613,7 @@
 5. 도시계획, 도시개발, 스마트도시, 건축 사업·행정, 건축 허가·신고 등 도시건축에 관한 사항(조신설2022.12.28.)</t>
       </text>
     </comment>
-    <comment ref="E331" authorId="0" shapeId="0">
+    <comment ref="E330" authorId="0" shapeId="0">
       <text>
         <t>1. 재난관리 종합기획ㆍ운영평가 총괄
 2. 재해복구지원 및 수습대책 총괄
@@ -14446,7 +14648,7 @@
 31. 25.]</t>
       </text>
     </comment>
-    <comment ref="E332" authorId="0" shapeId="0">
+    <comment ref="E331" authorId="0" shapeId="0">
       <text>
         <t>1. 환경관리 및 보전에 관한 사항1의
 2. 기후대기정책에 관한 사항
@@ -14455,7 +14657,7 @@
 5. 산림 및 녹지에 관한 사항</t>
       </text>
     </comment>
-    <comment ref="E333" authorId="0" shapeId="0">
+    <comment ref="E332" authorId="0" shapeId="0">
       <text>
         <t>1. 환경정책·환경평가에 관한 사항
 2. 세계환경수도 조성 및 총괄 조정 등에 관한 사항2의
@@ -14475,7 +14677,7 @@
 16. 산림정책·산림경영·산림보존·한라생태숲에 관한 사항[전문개정 2017.7.20.][제목개정 2022.12.30.][제20조에서 이동, 종전 제16조는 제13조로 이동 ]</t>
       </text>
     </comment>
-    <comment ref="E334" authorId="0" shapeId="0">
+    <comment ref="E333" authorId="0" shapeId="0">
       <text>
         <t>1. 농업정책 종합계획수립 및 추진
 2. 친환경농업 육성 계획 수립 및 추진
@@ -14492,7 +14694,7 @@
 13. 수의정책, 가축전염병 방역, 축산물 위생, 축산물 이력제 및 동물복지에 관한 사항[전문개정 2017.7.20.][제20조에서 이동 ]</t>
       </text>
     </comment>
-    <comment ref="E335" authorId="0" shapeId="0">
+    <comment ref="E334" authorId="0" shapeId="0">
       <text>
         <t>1. 광역폐기물처리시설 운영ㆍ관리
 2. 광역폐기물처리시설 주민편익시설 운영ㆍ관리
@@ -14792,7 +14994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R335"/>
+  <dimension ref="A1:W334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14813,6 +15015,11 @@
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -14907,6 +15114,31 @@
           <t>하위기구13</t>
         </is>
       </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>하위기구14</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>하위기구15</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>하위기구16</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>하위기구17</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>하위기구18</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -27350,36 +27582,121 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="3" t="inlineStr">
+      <c r="A251" s="7" t="inlineStr">
         <is>
           <t>36760</t>
         </is>
       </c>
-      <c r="B251" s="4" t="inlineStr">
+      <c r="B251" s="8" t="inlineStr">
         <is>
           <t>전라남도</t>
         </is>
       </c>
-      <c r="C251" s="4" t="inlineStr">
+      <c r="C251" s="8" t="inlineStr">
         <is>
           <t>화순군</t>
         </is>
       </c>
-      <c r="D251" s="3" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E251" s="4" t="inlineStr">
+      <c r="D251" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E251" s="8" t="inlineStr">
+        <is>
+          <t>보좌기관</t>
+        </is>
+      </c>
+      <c r="F251" s="5" t="inlineStr">
+        <is>
+          <t>홍보소통담당관</t>
+        </is>
+      </c>
+      <c r="G251" s="5" t="inlineStr">
+        <is>
+          <t>바이오백신담당관</t>
+        </is>
+      </c>
+      <c r="H251" s="5" t="inlineStr">
+        <is>
+          <t>인구청년정책과</t>
+        </is>
+      </c>
+      <c r="I251" s="5" t="inlineStr">
+        <is>
+          <t>주민안전과</t>
+        </is>
+      </c>
+      <c r="J251" s="5" t="inlineStr">
+        <is>
+          <t>지역경제과</t>
+        </is>
+      </c>
+      <c r="K251" s="5" t="inlineStr">
+        <is>
+          <t>행복민원과</t>
+        </is>
+      </c>
+      <c r="L251" s="5" t="inlineStr">
+        <is>
+          <t>인허가과</t>
+        </is>
+      </c>
+      <c r="M251" s="5" t="inlineStr">
+        <is>
+          <t>자치행정과</t>
+        </is>
+      </c>
+      <c r="N251" s="5" t="inlineStr">
+        <is>
+          <t>재무과</t>
+        </is>
+      </c>
+      <c r="O251" s="5" t="inlineStr">
+        <is>
+          <t>사회복지과</t>
+        </is>
+      </c>
+      <c r="P251" s="5" t="inlineStr">
+        <is>
+          <t>통합돌봄과</t>
+        </is>
+      </c>
+      <c r="Q251" s="5" t="inlineStr">
+        <is>
+          <t>문화예술과</t>
+        </is>
+      </c>
+      <c r="R251" s="5" t="inlineStr">
+        <is>
+          <t>농업정책과</t>
+        </is>
+      </c>
+      <c r="S251" s="5" t="inlineStr">
+        <is>
+          <t>농촌활력과</t>
+        </is>
+      </c>
+      <c r="T251" s="6" t="inlineStr">
         <is>
           <t>산림과</t>
+        </is>
+      </c>
+      <c r="U251" s="6" t="inlineStr">
+        <is>
+          <t>환경과</t>
+        </is>
+      </c>
+      <c r="V251" s="5" t="inlineStr">
+        <is>
+          <t>도시과</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>36760</t>
+          <t>36770</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
@@ -27389,7 +27706,7 @@
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>화순군</t>
+          <t>장흥군</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
@@ -27399,7 +27716,7 @@
       </c>
       <c r="E252" s="4" t="inlineStr">
         <is>
-          <t>환경과</t>
+          <t>환경관리과</t>
         </is>
       </c>
     </row>
@@ -27426,88 +27743,108 @@
       </c>
       <c r="E253" s="4" t="inlineStr">
         <is>
-          <t>환경관리과</t>
+          <t>산림휴양과</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="3" t="inlineStr">
-        <is>
-          <t>36770</t>
-        </is>
-      </c>
-      <c r="B254" s="4" t="inlineStr">
+      <c r="A254" s="7" t="inlineStr">
+        <is>
+          <t>36780</t>
+        </is>
+      </c>
+      <c r="B254" s="8" t="inlineStr">
         <is>
           <t>전라남도</t>
         </is>
       </c>
-      <c r="C254" s="4" t="inlineStr">
-        <is>
-          <t>장흥군</t>
-        </is>
-      </c>
-      <c r="D254" s="3" t="inlineStr">
+      <c r="C254" s="8" t="inlineStr">
+        <is>
+          <t>강진군</t>
+        </is>
+      </c>
+      <c r="D254" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E254" s="8" t="inlineStr">
+        <is>
+          <t>농림축수산국</t>
+        </is>
+      </c>
+      <c r="F254" s="5" t="inlineStr">
+        <is>
+          <t>농정과</t>
+        </is>
+      </c>
+      <c r="G254" s="6" t="inlineStr">
+        <is>
+          <t>산림과</t>
+        </is>
+      </c>
+      <c r="H254" s="5" t="inlineStr">
+        <is>
+          <t>축산과</t>
+        </is>
+      </c>
+      <c r="I254" s="5" t="inlineStr">
+        <is>
+          <t>해양수산과</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>36780</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>전라남도</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>강진군</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="E254" s="4" t="inlineStr">
-        <is>
-          <t>산림휴양과</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="7" t="inlineStr">
-        <is>
-          <t>36780</t>
-        </is>
-      </c>
-      <c r="B255" s="8" t="inlineStr">
-        <is>
-          <t>전라남도</t>
-        </is>
-      </c>
-      <c r="C255" s="8" t="inlineStr">
-        <is>
-          <t>강진군</t>
-        </is>
-      </c>
-      <c r="D255" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E255" s="8" t="inlineStr">
-        <is>
-          <t>농림축수산국</t>
+      <c r="E255" s="4" t="inlineStr">
+        <is>
+          <t>복지환경국</t>
         </is>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>농정과</t>
-        </is>
-      </c>
-      <c r="G255" s="6" t="inlineStr">
-        <is>
-          <t>산림과</t>
-        </is>
-      </c>
-      <c r="H255" s="5" t="inlineStr">
-        <is>
-          <t>축산과</t>
+          <t>주민복지과</t>
+        </is>
+      </c>
+      <c r="G255" s="5" t="inlineStr">
+        <is>
+          <t>군민행복과</t>
+        </is>
+      </c>
+      <c r="H255" s="6" t="inlineStr">
+        <is>
+          <t>환경과</t>
         </is>
       </c>
       <c r="I255" s="5" t="inlineStr">
         <is>
-          <t>해양수산과</t>
+          <t>민원봉사과</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>36780</t>
+          <t>36790</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
@@ -27517,7 +27854,7 @@
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>강진군</t>
+          <t>해남군</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -27527,27 +27864,7 @@
       </c>
       <c r="E256" s="4" t="inlineStr">
         <is>
-          <t>복지환경국</t>
-        </is>
-      </c>
-      <c r="F256" s="5" t="inlineStr">
-        <is>
-          <t>주민복지과</t>
-        </is>
-      </c>
-      <c r="G256" s="5" t="inlineStr">
-        <is>
-          <t>군민행복과</t>
-        </is>
-      </c>
-      <c r="H256" s="6" t="inlineStr">
-        <is>
           <t>환경과</t>
-        </is>
-      </c>
-      <c r="I256" s="5" t="inlineStr">
-        <is>
-          <t>민원봉사과</t>
         </is>
       </c>
     </row>
@@ -27574,98 +27891,123 @@
       </c>
       <c r="E257" s="4" t="inlineStr">
         <is>
-          <t>환경과</t>
+          <t>산림공원과</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="3" t="inlineStr">
-        <is>
-          <t>36790</t>
-        </is>
-      </c>
-      <c r="B258" s="4" t="inlineStr">
+      <c r="A258" s="7" t="inlineStr">
+        <is>
+          <t>36800</t>
+        </is>
+      </c>
+      <c r="B258" s="8" t="inlineStr">
         <is>
           <t>전라남도</t>
         </is>
       </c>
-      <c r="C258" s="4" t="inlineStr">
-        <is>
-          <t>해남군</t>
-        </is>
-      </c>
-      <c r="D258" s="3" t="inlineStr">
+      <c r="C258" s="8" t="inlineStr">
+        <is>
+          <t>영암군</t>
+        </is>
+      </c>
+      <c r="D258" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E258" s="8" t="inlineStr">
+        <is>
+          <t>농업경제국</t>
+        </is>
+      </c>
+      <c r="F258" s="5" t="inlineStr">
+        <is>
+          <t>농업정책과</t>
+        </is>
+      </c>
+      <c r="G258" s="5" t="inlineStr">
+        <is>
+          <t>축산과</t>
+        </is>
+      </c>
+      <c r="H258" s="5" t="inlineStr">
+        <is>
+          <t>유통산업과</t>
+        </is>
+      </c>
+      <c r="I258" s="6" t="inlineStr">
+        <is>
+          <t>산림휴양과</t>
+        </is>
+      </c>
+      <c r="J258" s="6" t="inlineStr">
+        <is>
+          <t>지역순환경제과</t>
+        </is>
+      </c>
+      <c r="K258" s="5" t="inlineStr">
+        <is>
+          <t>도시디자인과</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>36800</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>전라남도</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>영암군</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="E258" s="4" t="inlineStr">
-        <is>
-          <t>산림공원과</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="7" t="inlineStr">
-        <is>
-          <t>36800</t>
-        </is>
-      </c>
-      <c r="B259" s="8" t="inlineStr">
-        <is>
-          <t>전라남도</t>
-        </is>
-      </c>
-      <c r="C259" s="8" t="inlineStr">
-        <is>
-          <t>영암군</t>
-        </is>
-      </c>
-      <c r="D259" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E259" s="8" t="inlineStr">
-        <is>
-          <t>농업경제국</t>
+      <c r="E259" s="4" t="inlineStr">
+        <is>
+          <t>안전건설환경국</t>
         </is>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>농업정책과</t>
+          <t>군민안전과</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>축산과</t>
+          <t>건설교통과</t>
         </is>
       </c>
       <c r="H259" s="5" t="inlineStr">
         <is>
-          <t>유통산업과</t>
+          <t>도시디자인과</t>
         </is>
       </c>
       <c r="I259" s="6" t="inlineStr">
         <is>
-          <t>산림휴양과</t>
-        </is>
-      </c>
-      <c r="J259" s="6" t="inlineStr">
-        <is>
-          <t>지역순환경제과</t>
-        </is>
-      </c>
-      <c r="K259" s="5" t="inlineStr">
-        <is>
-          <t>도시디자인과</t>
+          <t>환경기후과</t>
+        </is>
+      </c>
+      <c r="J259" s="5" t="inlineStr">
+        <is>
+          <t>공영개발사업단</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>36800</t>
+          <t>36810</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
@@ -27675,7 +28017,7 @@
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>영암군</t>
+          <t>무안군</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -27685,32 +28027,7 @@
       </c>
       <c r="E260" s="4" t="inlineStr">
         <is>
-          <t>안전건설환경국</t>
-        </is>
-      </c>
-      <c r="F260" s="5" t="inlineStr">
-        <is>
-          <t>군민안전과</t>
-        </is>
-      </c>
-      <c r="G260" s="5" t="inlineStr">
-        <is>
-          <t>건설교통과</t>
-        </is>
-      </c>
-      <c r="H260" s="5" t="inlineStr">
-        <is>
-          <t>도시디자인과</t>
-        </is>
-      </c>
-      <c r="I260" s="6" t="inlineStr">
-        <is>
-          <t>환경기후과</t>
-        </is>
-      </c>
-      <c r="J260" s="5" t="inlineStr">
-        <is>
-          <t>공영개발사업단</t>
+          <t>환경과</t>
         </is>
       </c>
     </row>
@@ -27737,14 +28054,14 @@
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t>환경과</t>
+          <t>산림공원과</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>36810</t>
+          <t>36820</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
@@ -27754,7 +28071,7 @@
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>무안군</t>
+          <t>함평군</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -27764,7 +28081,7 @@
       </c>
       <c r="E262" s="4" t="inlineStr">
         <is>
-          <t>산림공원과</t>
+          <t>환경관리과</t>
         </is>
       </c>
     </row>
@@ -27791,7 +28108,7 @@
       </c>
       <c r="E263" s="4" t="inlineStr">
         <is>
-          <t>환경관리과</t>
+          <t>산림공원과</t>
         </is>
       </c>
     </row>
@@ -27818,7 +28135,7 @@
       </c>
       <c r="E264" s="4" t="inlineStr">
         <is>
-          <t>산림공원과</t>
+          <t>맑은물사업소</t>
         </is>
       </c>
     </row>
@@ -28033,36 +28350,126 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="3" t="inlineStr">
+      <c r="A270" s="7" t="inlineStr">
         <is>
           <t>36850</t>
         </is>
       </c>
-      <c r="B270" s="4" t="inlineStr">
+      <c r="B270" s="8" t="inlineStr">
         <is>
           <t>전라남도</t>
         </is>
       </c>
-      <c r="C270" s="4" t="inlineStr">
+      <c r="C270" s="8" t="inlineStr">
         <is>
           <t>완도군</t>
         </is>
       </c>
-      <c r="D270" s="3" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E270" s="4" t="inlineStr">
+      <c r="D270" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E270" s="8" t="inlineStr">
+        <is>
+          <t>보좌기관</t>
+        </is>
+      </c>
+      <c r="F270" s="5" t="inlineStr">
+        <is>
+          <t>해양치유담당관</t>
+        </is>
+      </c>
+      <c r="G270" s="5" t="inlineStr">
+        <is>
+          <t>행정지원과</t>
+        </is>
+      </c>
+      <c r="H270" s="5" t="inlineStr">
+        <is>
+          <t>세무회계과</t>
+        </is>
+      </c>
+      <c r="I270" s="5" t="inlineStr">
+        <is>
+          <t>민원봉사과</t>
+        </is>
+      </c>
+      <c r="J270" s="5" t="inlineStr">
+        <is>
+          <t>주민복지과</t>
+        </is>
+      </c>
+      <c r="K270" s="5" t="inlineStr">
+        <is>
+          <t>가족행복과</t>
+        </is>
+      </c>
+      <c r="L270" s="5" t="inlineStr">
+        <is>
+          <t>경제교통과</t>
+        </is>
+      </c>
+      <c r="M270" s="5" t="inlineStr">
+        <is>
+          <t>문화예술과</t>
+        </is>
+      </c>
+      <c r="N270" s="5" t="inlineStr">
+        <is>
+          <t>체육진흥과</t>
+        </is>
+      </c>
+      <c r="O270" s="5" t="inlineStr">
+        <is>
+          <t>농업축산과</t>
+        </is>
+      </c>
+      <c r="P270" s="5" t="inlineStr">
+        <is>
+          <t>해양정책과</t>
+        </is>
+      </c>
+      <c r="Q270" s="5" t="inlineStr">
+        <is>
+          <t>해조류박람회추진단</t>
+        </is>
+      </c>
+      <c r="R270" s="5" t="inlineStr">
+        <is>
+          <t>수산경영과</t>
+        </is>
+      </c>
+      <c r="S270" s="6" t="inlineStr">
         <is>
           <t>산림휴양과</t>
+        </is>
+      </c>
+      <c r="T270" s="6" t="inlineStr">
+        <is>
+          <t>환경수질관리과</t>
+        </is>
+      </c>
+      <c r="U270" s="5" t="inlineStr">
+        <is>
+          <t>지역개발과</t>
+        </is>
+      </c>
+      <c r="V270" s="5" t="inlineStr">
+        <is>
+          <t>건설과</t>
+        </is>
+      </c>
+      <c r="W270" s="5" t="inlineStr">
+        <is>
+          <t>안전총괄과</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>36850</t>
+          <t>36860</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
@@ -28072,7 +28479,7 @@
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>완도군</t>
+          <t>진도군</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -28082,7 +28489,7 @@
       </c>
       <c r="E271" s="4" t="inlineStr">
         <is>
-          <t>환경수질관리과</t>
+          <t>환경수질과</t>
         </is>
       </c>
     </row>
@@ -28109,34 +28516,60 @@
       </c>
       <c r="E272" s="4" t="inlineStr">
         <is>
-          <t>환경수질과</t>
+          <t>산림휴양과</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="3" t="inlineStr">
-        <is>
-          <t>36860</t>
-        </is>
-      </c>
-      <c r="B273" s="4" t="inlineStr">
+      <c r="A273" s="7" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B273" s="8" t="inlineStr">
         <is>
           <t>전라남도</t>
         </is>
       </c>
-      <c r="C273" s="4" t="inlineStr">
-        <is>
-          <t>진도군</t>
-        </is>
-      </c>
-      <c r="D273" s="3" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E273" s="4" t="inlineStr">
-        <is>
-          <t>산림휴양과</t>
+      <c r="C273" s="8" t="inlineStr"/>
+      <c r="D273" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E273" s="8" t="inlineStr">
+        <is>
+          <t>농축산식품국</t>
+        </is>
+      </c>
+      <c r="F273" s="5" t="inlineStr">
+        <is>
+          <t>농업정책과</t>
+        </is>
+      </c>
+      <c r="G273" s="6" t="inlineStr">
+        <is>
+          <t>친환경농업과</t>
+        </is>
+      </c>
+      <c r="H273" s="5" t="inlineStr">
+        <is>
+          <t>식량원예과</t>
+        </is>
+      </c>
+      <c r="I273" s="5" t="inlineStr">
+        <is>
+          <t>농식품유통과</t>
+        </is>
+      </c>
+      <c r="J273" s="5" t="inlineStr">
+        <is>
+          <t>축산정책과</t>
+        </is>
+      </c>
+      <c r="K273" s="5" t="inlineStr">
+        <is>
+          <t>동물방역과</t>
         </is>
       </c>
     </row>
@@ -28159,95 +28592,94 @@
       </c>
       <c r="E274" s="8" t="inlineStr">
         <is>
-          <t>농축산식품국</t>
+          <t>해양수산국</t>
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>농업정책과</t>
-        </is>
-      </c>
-      <c r="G274" s="6" t="inlineStr">
-        <is>
-          <t>친환경농업과</t>
-        </is>
-      </c>
-      <c r="H274" s="5" t="inlineStr">
-        <is>
-          <t>식량원예과</t>
+          <t>해운항만과</t>
+        </is>
+      </c>
+      <c r="G274" s="5" t="inlineStr">
+        <is>
+          <t>섬해양정책과</t>
+        </is>
+      </c>
+      <c r="H274" s="6" t="inlineStr">
+        <is>
+          <t>친환경수산과</t>
         </is>
       </c>
       <c r="I274" s="5" t="inlineStr">
         <is>
-          <t>농식품유통과</t>
-        </is>
-      </c>
-      <c r="J274" s="5" t="inlineStr">
-        <is>
-          <t>축산정책과</t>
-        </is>
-      </c>
-      <c r="K274" s="5" t="inlineStr">
-        <is>
-          <t>동물방역과</t>
+          <t>수산유통가공과</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="7" t="inlineStr">
+      <c r="A275" s="3" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B275" s="8" t="inlineStr">
+      <c r="B275" s="4" t="inlineStr">
         <is>
           <t>전라남도</t>
         </is>
       </c>
-      <c r="C275" s="8" t="inlineStr"/>
-      <c r="D275" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E275" s="8" t="inlineStr">
-        <is>
-          <t>해양수산국</t>
-        </is>
-      </c>
-      <c r="F275" s="5" t="inlineStr">
-        <is>
-          <t>해운항만과</t>
-        </is>
-      </c>
-      <c r="G275" s="5" t="inlineStr">
-        <is>
-          <t>섬해양정책과</t>
-        </is>
-      </c>
-      <c r="H275" s="6" t="inlineStr">
-        <is>
-          <t>친환경수산과</t>
-        </is>
-      </c>
-      <c r="I275" s="5" t="inlineStr">
-        <is>
-          <t>수산유통가공과</t>
+      <c r="C275" s="4" t="inlineStr"/>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E275" s="4" t="inlineStr">
+        <is>
+          <t>환경산림국</t>
+        </is>
+      </c>
+      <c r="F275" s="6" t="inlineStr">
+        <is>
+          <t>환경정책과</t>
+        </is>
+      </c>
+      <c r="G275" s="6" t="inlineStr">
+        <is>
+          <t>기후대기과</t>
+        </is>
+      </c>
+      <c r="H275" s="5" t="inlineStr">
+        <is>
+          <t>수자원관리과</t>
+        </is>
+      </c>
+      <c r="I275" s="6" t="inlineStr">
+        <is>
+          <t>산림자원과</t>
+        </is>
+      </c>
+      <c r="J275" s="6" t="inlineStr">
+        <is>
+          <t>산림휴양과</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37010</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>전라남도</t>
-        </is>
-      </c>
-      <c r="C276" s="4" t="inlineStr"/>
+          <t>경상북도</t>
+        </is>
+      </c>
+      <c r="C276" s="4" t="inlineStr">
+        <is>
+          <t>포항시</t>
+        </is>
+      </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
           <t>○</t>
@@ -28255,7 +28687,7 @@
       </c>
       <c r="E276" s="4" t="inlineStr">
         <is>
-          <t>환경산림국</t>
+          <t>환경국</t>
         </is>
       </c>
       <c r="F276" s="6" t="inlineStr">
@@ -28270,24 +28702,19 @@
       </c>
       <c r="H276" s="5" t="inlineStr">
         <is>
-          <t>수자원관리과</t>
-        </is>
-      </c>
-      <c r="I276" s="6" t="inlineStr">
-        <is>
-          <t>산림자원과</t>
-        </is>
-      </c>
-      <c r="J276" s="6" t="inlineStr">
-        <is>
-          <t>산림휴양과</t>
+          <t>자원순환과</t>
+        </is>
+      </c>
+      <c r="I276" s="5" t="inlineStr">
+        <is>
+          <t>식품산업과</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>37010</t>
+          <t>37020</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
@@ -28297,7 +28724,7 @@
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>포항시</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -28307,7 +28734,7 @@
       </c>
       <c r="E277" s="4" t="inlineStr">
         <is>
-          <t>환경국</t>
+          <t>환경녹지국</t>
         </is>
       </c>
       <c r="F277" s="6" t="inlineStr">
@@ -28315,26 +28742,31 @@
           <t>환경정책과</t>
         </is>
       </c>
-      <c r="G277" s="6" t="inlineStr">
-        <is>
-          <t>기후대기과</t>
-        </is>
-      </c>
-      <c r="H277" s="5" t="inlineStr">
+      <c r="G277" s="5" t="inlineStr">
         <is>
           <t>자원순환과</t>
         </is>
       </c>
+      <c r="H277" s="6" t="inlineStr">
+        <is>
+          <t>산림경영과</t>
+        </is>
+      </c>
       <c r="I277" s="5" t="inlineStr">
         <is>
-          <t>식품산업과</t>
+          <t>도시공원과</t>
+        </is>
+      </c>
+      <c r="J277" s="5" t="inlineStr">
+        <is>
+          <t>토지정보과</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>37020</t>
+          <t>37030</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
@@ -28344,7 +28776,7 @@
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>김천시</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
@@ -28359,34 +28791,34 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>환경정책과</t>
-        </is>
-      </c>
-      <c r="G278" s="5" t="inlineStr">
+          <t>기후에너지과</t>
+        </is>
+      </c>
+      <c r="G278" s="6" t="inlineStr">
+        <is>
+          <t>산림과</t>
+        </is>
+      </c>
+      <c r="H278" s="5" t="inlineStr">
+        <is>
+          <t>상하수도과</t>
+        </is>
+      </c>
+      <c r="I278" s="6" t="inlineStr">
+        <is>
+          <t>환경위생과</t>
+        </is>
+      </c>
+      <c r="J278" s="5" t="inlineStr">
         <is>
           <t>자원순환과</t>
-        </is>
-      </c>
-      <c r="H278" s="6" t="inlineStr">
-        <is>
-          <t>산림경영과</t>
-        </is>
-      </c>
-      <c r="I278" s="5" t="inlineStr">
-        <is>
-          <t>도시공원과</t>
-        </is>
-      </c>
-      <c r="J278" s="5" t="inlineStr">
-        <is>
-          <t>토지정보과</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>37030</t>
+          <t>37040</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
@@ -28396,7 +28828,7 @@
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>김천시</t>
+          <t>안동시</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -28406,32 +28838,32 @@
       </c>
       <c r="E279" s="4" t="inlineStr">
         <is>
-          <t>환경녹지국</t>
-        </is>
-      </c>
-      <c r="F279" s="6" t="inlineStr">
-        <is>
-          <t>기후에너지과</t>
+          <t>수자원환경국</t>
+        </is>
+      </c>
+      <c r="F279" s="5" t="inlineStr">
+        <is>
+          <t>수자원정책과</t>
         </is>
       </c>
       <c r="G279" s="6" t="inlineStr">
         <is>
+          <t>환경관리과</t>
+        </is>
+      </c>
+      <c r="H279" s="5" t="inlineStr">
+        <is>
+          <t>자원순환과</t>
+        </is>
+      </c>
+      <c r="I279" s="6" t="inlineStr">
+        <is>
           <t>산림과</t>
         </is>
       </c>
-      <c r="H279" s="5" t="inlineStr">
-        <is>
-          <t>상하수도과</t>
-        </is>
-      </c>
-      <c r="I279" s="6" t="inlineStr">
-        <is>
-          <t>환경위생과</t>
-        </is>
-      </c>
       <c r="J279" s="5" t="inlineStr">
         <is>
-          <t>자원순환과</t>
+          <t>공원녹지과</t>
         </is>
       </c>
     </row>
@@ -28458,39 +28890,34 @@
       </c>
       <c r="E280" s="4" t="inlineStr">
         <is>
-          <t>수자원환경국</t>
-        </is>
-      </c>
-      <c r="F280" s="5" t="inlineStr">
-        <is>
-          <t>수자원정책과</t>
-        </is>
-      </c>
-      <c r="G280" s="6" t="inlineStr">
-        <is>
-          <t>환경관리과</t>
+          <t>맑은물사업국</t>
+        </is>
+      </c>
+      <c r="F280" s="6" t="inlineStr">
+        <is>
+          <t>맑은물정책과</t>
+        </is>
+      </c>
+      <c r="G280" s="5" t="inlineStr">
+        <is>
+          <t>상수도과</t>
         </is>
       </c>
       <c r="H280" s="5" t="inlineStr">
         <is>
-          <t>자원순환과</t>
+          <t>하수도과</t>
         </is>
       </c>
       <c r="I280" s="6" t="inlineStr">
         <is>
-          <t>산림과</t>
-        </is>
-      </c>
-      <c r="J280" s="5" t="inlineStr">
-        <is>
-          <t>공원녹지과</t>
+          <t>맑은물관리과</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>37040</t>
+          <t>37050</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
@@ -28500,7 +28927,7 @@
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>안동시</t>
+          <t>구미시</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
@@ -28510,200 +28937,215 @@
       </c>
       <c r="E281" s="4" t="inlineStr">
         <is>
-          <t>맑은물사업국</t>
+          <t>환경교통국</t>
         </is>
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>맑은물정책과</t>
-        </is>
-      </c>
-      <c r="G281" s="5" t="inlineStr">
-        <is>
-          <t>상수도과</t>
+          <t>환경정책과</t>
+        </is>
+      </c>
+      <c r="G281" s="6" t="inlineStr">
+        <is>
+          <t>환경관리과</t>
         </is>
       </c>
       <c r="H281" s="5" t="inlineStr">
         <is>
-          <t>하수도과</t>
-        </is>
-      </c>
-      <c r="I281" s="6" t="inlineStr">
-        <is>
-          <t>맑은물관리과</t>
+          <t>교통정책과</t>
+        </is>
+      </c>
+      <c r="I281" s="5" t="inlineStr">
+        <is>
+          <t>대중교통과</t>
+        </is>
+      </c>
+      <c r="J281" s="5" t="inlineStr">
+        <is>
+          <t>공원녹지과</t>
+        </is>
+      </c>
+      <c r="K281" s="5" t="inlineStr">
+        <is>
+          <t>자원순환과</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="3" t="inlineStr">
-        <is>
-          <t>37050</t>
-        </is>
-      </c>
-      <c r="B282" s="4" t="inlineStr">
+      <c r="A282" s="7" t="inlineStr">
+        <is>
+          <t>37060</t>
+        </is>
+      </c>
+      <c r="B282" s="8" t="inlineStr">
         <is>
           <t>경상북도</t>
         </is>
       </c>
-      <c r="C282" s="4" t="inlineStr">
-        <is>
-          <t>구미시</t>
-        </is>
-      </c>
-      <c r="D282" s="3" t="inlineStr">
+      <c r="C282" s="8" t="inlineStr">
+        <is>
+          <t>영주시</t>
+        </is>
+      </c>
+      <c r="D282" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E282" s="8" t="inlineStr">
+        <is>
+          <t>경제산업국</t>
+        </is>
+      </c>
+      <c r="F282" s="5" t="inlineStr">
+        <is>
+          <t>일자리경제과</t>
+        </is>
+      </c>
+      <c r="G282" s="5" t="inlineStr">
+        <is>
+          <t>투자유치과</t>
+        </is>
+      </c>
+      <c r="H282" s="6" t="inlineStr">
+        <is>
+          <t>환경보호과</t>
+        </is>
+      </c>
+      <c r="I282" s="5" t="inlineStr">
+        <is>
+          <t>교통행정과</t>
+        </is>
+      </c>
+      <c r="J282" s="6" t="inlineStr">
+        <is>
+          <t>산림과</t>
+        </is>
+      </c>
+      <c r="K282" s="5" t="inlineStr">
+        <is>
+          <t>공원관리과</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>37070</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="inlineStr">
+        <is>
+          <t>경상북도</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr">
+        <is>
+          <t>영천시</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="E282" s="4" t="inlineStr">
-        <is>
-          <t>환경교통국</t>
-        </is>
-      </c>
-      <c r="F282" s="6" t="inlineStr">
-        <is>
-          <t>환경정책과</t>
-        </is>
-      </c>
-      <c r="G282" s="6" t="inlineStr">
+      <c r="E283" s="4" t="inlineStr">
+        <is>
+          <t>경제환경산업국</t>
+        </is>
+      </c>
+      <c r="F283" s="5" t="inlineStr">
+        <is>
+          <t>일자리노사과</t>
+        </is>
+      </c>
+      <c r="G283" s="5" t="inlineStr">
+        <is>
+          <t>기업유치과</t>
+        </is>
+      </c>
+      <c r="H283" s="6" t="inlineStr">
+        <is>
+          <t>환경보호과</t>
+        </is>
+      </c>
+      <c r="I283" s="5" t="inlineStr">
+        <is>
+          <t>자원순환과</t>
+        </is>
+      </c>
+      <c r="J283" s="6" t="inlineStr">
+        <is>
+          <t>산림과</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="7" t="inlineStr">
+        <is>
+          <t>37080</t>
+        </is>
+      </c>
+      <c r="B284" s="8" t="inlineStr">
+        <is>
+          <t>경상북도</t>
+        </is>
+      </c>
+      <c r="C284" s="8" t="inlineStr">
+        <is>
+          <t>상주시</t>
+        </is>
+      </c>
+      <c r="D284" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E284" s="8" t="inlineStr">
+        <is>
+          <t>경제산업국</t>
+        </is>
+      </c>
+      <c r="F284" s="5" t="inlineStr">
+        <is>
+          <t>투자경제과</t>
+        </is>
+      </c>
+      <c r="G284" s="6" t="inlineStr">
         <is>
           <t>환경관리과</t>
         </is>
       </c>
-      <c r="H282" s="5" t="inlineStr">
-        <is>
-          <t>교통정책과</t>
-        </is>
-      </c>
-      <c r="I282" s="5" t="inlineStr">
-        <is>
-          <t>대중교통과</t>
-        </is>
-      </c>
-      <c r="J282" s="5" t="inlineStr">
-        <is>
-          <t>공원녹지과</t>
-        </is>
-      </c>
-      <c r="K282" s="5" t="inlineStr">
-        <is>
-          <t>자원순환과</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="7" t="inlineStr">
-        <is>
-          <t>37060</t>
-        </is>
-      </c>
-      <c r="B283" s="8" t="inlineStr">
-        <is>
-          <t>경상북도</t>
-        </is>
-      </c>
-      <c r="C283" s="8" t="inlineStr">
-        <is>
-          <t>영주시</t>
-        </is>
-      </c>
-      <c r="D283" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E283" s="8" t="inlineStr">
-        <is>
-          <t>경제산업국</t>
-        </is>
-      </c>
-      <c r="F283" s="5" t="inlineStr">
-        <is>
-          <t>일자리경제과</t>
-        </is>
-      </c>
-      <c r="G283" s="5" t="inlineStr">
-        <is>
-          <t>투자유치과</t>
-        </is>
-      </c>
-      <c r="H283" s="6" t="inlineStr">
-        <is>
-          <t>환경보호과</t>
-        </is>
-      </c>
-      <c r="I283" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과</t>
-        </is>
-      </c>
-      <c r="J283" s="6" t="inlineStr">
-        <is>
-          <t>산림과</t>
-        </is>
-      </c>
-      <c r="K283" s="5" t="inlineStr">
-        <is>
-          <t>공원관리과</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="3" t="inlineStr">
-        <is>
-          <t>37070</t>
-        </is>
-      </c>
-      <c r="B284" s="4" t="inlineStr">
-        <is>
-          <t>경상북도</t>
-        </is>
-      </c>
-      <c r="C284" s="4" t="inlineStr">
-        <is>
-          <t>영천시</t>
-        </is>
-      </c>
-      <c r="D284" s="3" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E284" s="4" t="inlineStr">
-        <is>
-          <t>경제환경산업국</t>
-        </is>
-      </c>
-      <c r="F284" s="5" t="inlineStr">
-        <is>
-          <t>일자리노사과</t>
-        </is>
-      </c>
-      <c r="G284" s="5" t="inlineStr">
-        <is>
-          <t>기업유치과</t>
-        </is>
-      </c>
-      <c r="H284" s="6" t="inlineStr">
-        <is>
-          <t>환경보호과</t>
+      <c r="H284" s="5" t="inlineStr">
+        <is>
+          <t>농업정책과</t>
         </is>
       </c>
       <c r="I284" s="5" t="inlineStr">
         <is>
-          <t>자원순환과</t>
-        </is>
-      </c>
-      <c r="J284" s="6" t="inlineStr">
-        <is>
-          <t>산림과</t>
+          <t>스마트농업과</t>
+        </is>
+      </c>
+      <c r="J284" s="5" t="inlineStr">
+        <is>
+          <t>축산과</t>
+        </is>
+      </c>
+      <c r="K284" s="5" t="inlineStr">
+        <is>
+          <t>유통마케팅과</t>
+        </is>
+      </c>
+      <c r="L284" s="6" t="inlineStr">
+        <is>
+          <t>산림녹지과</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>37080</t>
+          <t>37090</t>
         </is>
       </c>
       <c r="B285" s="8" t="inlineStr">
@@ -28713,7 +29155,7 @@
       </c>
       <c r="C285" s="8" t="inlineStr">
         <is>
-          <t>상주시</t>
+          <t>문경시</t>
         </is>
       </c>
       <c r="D285" s="7" t="inlineStr">
@@ -28723,37 +29165,37 @@
       </c>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>경제산업국</t>
+          <t>문화관광농업국</t>
         </is>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>투자경제과</t>
-        </is>
-      </c>
-      <c r="G285" s="6" t="inlineStr">
-        <is>
-          <t>환경관리과</t>
+          <t>문화예술과</t>
+        </is>
+      </c>
+      <c r="G285" s="5" t="inlineStr">
+        <is>
+          <t>관광진흥과</t>
         </is>
       </c>
       <c r="H285" s="5" t="inlineStr">
         <is>
-          <t>농업정책과</t>
+          <t>식품위생과</t>
         </is>
       </c>
       <c r="I285" s="5" t="inlineStr">
         <is>
-          <t>스마트농업과</t>
+          <t>농정과</t>
         </is>
       </c>
       <c r="J285" s="5" t="inlineStr">
         <is>
-          <t>축산과</t>
+          <t>유통축산과</t>
         </is>
       </c>
       <c r="K285" s="5" t="inlineStr">
         <is>
-          <t>유통마케팅과</t>
+          <t>지역활력과</t>
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr">
@@ -28785,69 +29227,74 @@
       </c>
       <c r="E286" s="8" t="inlineStr">
         <is>
-          <t>문화관광농업국</t>
+          <t>경제도시국</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>문화예술과</t>
-        </is>
-      </c>
-      <c r="G286" s="5" t="inlineStr">
-        <is>
-          <t>관광진흥과</t>
+          <t>일자리경제과</t>
+        </is>
+      </c>
+      <c r="G286" s="6" t="inlineStr">
+        <is>
+          <t>환경보호과</t>
         </is>
       </c>
       <c r="H286" s="5" t="inlineStr">
         <is>
-          <t>식품위생과</t>
+          <t>교통행정과</t>
         </is>
       </c>
       <c r="I286" s="5" t="inlineStr">
         <is>
-          <t>농정과</t>
+          <t>건설과</t>
         </is>
       </c>
       <c r="J286" s="5" t="inlineStr">
         <is>
-          <t>유통축산과</t>
+          <t>도시과</t>
         </is>
       </c>
       <c r="K286" s="5" t="inlineStr">
         <is>
-          <t>지역활력과</t>
-        </is>
-      </c>
-      <c r="L286" s="6" t="inlineStr">
-        <is>
-          <t>산림녹지과</t>
+          <t>안전재난과</t>
+        </is>
+      </c>
+      <c r="L286" s="5" t="inlineStr">
+        <is>
+          <t>건축과</t>
+        </is>
+      </c>
+      <c r="M286" s="5" t="inlineStr">
+        <is>
+          <t>허가과</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="7" t="inlineStr">
-        <is>
-          <t>37090</t>
-        </is>
-      </c>
-      <c r="B287" s="8" t="inlineStr">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>37100</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="inlineStr">
         <is>
           <t>경상북도</t>
         </is>
       </c>
-      <c r="C287" s="8" t="inlineStr">
-        <is>
-          <t>문경시</t>
-        </is>
-      </c>
-      <c r="D287" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E287" s="8" t="inlineStr">
-        <is>
-          <t>경제도시국</t>
+      <c r="C287" s="4" t="inlineStr">
+        <is>
+          <t>경산시</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E287" s="4" t="inlineStr">
+        <is>
+          <t>경제환경국</t>
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr">
@@ -28855,46 +29302,36 @@
           <t>일자리경제과</t>
         </is>
       </c>
-      <c r="G287" s="6" t="inlineStr">
-        <is>
-          <t>환경보호과</t>
-        </is>
-      </c>
-      <c r="H287" s="5" t="inlineStr">
+      <c r="G287" s="5" t="inlineStr">
         <is>
           <t>교통행정과</t>
         </is>
       </c>
+      <c r="H287" s="6" t="inlineStr">
+        <is>
+          <t>산림과</t>
+        </is>
+      </c>
       <c r="I287" s="5" t="inlineStr">
         <is>
-          <t>건설과</t>
-        </is>
-      </c>
-      <c r="J287" s="5" t="inlineStr">
-        <is>
-          <t>도시과</t>
+          <t>공원녹지과</t>
+        </is>
+      </c>
+      <c r="J287" s="6" t="inlineStr">
+        <is>
+          <t>환경과</t>
         </is>
       </c>
       <c r="K287" s="5" t="inlineStr">
         <is>
-          <t>안전재난과</t>
-        </is>
-      </c>
-      <c r="L287" s="5" t="inlineStr">
-        <is>
-          <t>건축과</t>
-        </is>
-      </c>
-      <c r="M287" s="5" t="inlineStr">
-        <is>
-          <t>허가과</t>
+          <t>자원순환과</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>37710</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
@@ -28904,7 +29341,7 @@
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>의성군</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
@@ -28914,44 +29351,44 @@
       </c>
       <c r="E288" s="4" t="inlineStr">
         <is>
-          <t>경제환경국</t>
+          <t>안전환경국</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>일자리경제과</t>
+          <t>안전건설과</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>교통행정과</t>
-        </is>
-      </c>
-      <c r="H288" s="6" t="inlineStr">
-        <is>
-          <t>산림과</t>
+          <t>농촌활력과</t>
+        </is>
+      </c>
+      <c r="H288" s="5" t="inlineStr">
+        <is>
+          <t>신공항지원과</t>
         </is>
       </c>
       <c r="I288" s="5" t="inlineStr">
         <is>
-          <t>공원녹지과</t>
+          <t>건축과</t>
         </is>
       </c>
       <c r="J288" s="6" t="inlineStr">
         <is>
-          <t>환경과</t>
-        </is>
-      </c>
-      <c r="K288" s="5" t="inlineStr">
-        <is>
-          <t>자원순환과</t>
+          <t>환경축산과</t>
+        </is>
+      </c>
+      <c r="K288" s="6" t="inlineStr">
+        <is>
+          <t>산림녹지과</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>37710</t>
+          <t>37720</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
@@ -28961,7 +29398,7 @@
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>의성군</t>
+          <t>청송군</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
@@ -28971,37 +29408,7 @@
       </c>
       <c r="E289" s="4" t="inlineStr">
         <is>
-          <t>안전환경국</t>
-        </is>
-      </c>
-      <c r="F289" s="5" t="inlineStr">
-        <is>
-          <t>안전건설과</t>
-        </is>
-      </c>
-      <c r="G289" s="5" t="inlineStr">
-        <is>
-          <t>농촌활력과</t>
-        </is>
-      </c>
-      <c r="H289" s="5" t="inlineStr">
-        <is>
-          <t>신공항지원과</t>
-        </is>
-      </c>
-      <c r="I289" s="5" t="inlineStr">
-        <is>
-          <t>건축과</t>
-        </is>
-      </c>
-      <c r="J289" s="6" t="inlineStr">
-        <is>
-          <t>환경축산과</t>
-        </is>
-      </c>
-      <c r="K289" s="6" t="inlineStr">
-        <is>
-          <t>산림녹지과</t>
+          <t>산림자원과</t>
         </is>
       </c>
     </row>
@@ -29028,34 +29435,54 @@
       </c>
       <c r="E290" s="4" t="inlineStr">
         <is>
-          <t>산림자원과</t>
+          <t>환경관리과</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="3" t="inlineStr">
-        <is>
-          <t>37720</t>
-        </is>
-      </c>
-      <c r="B291" s="4" t="inlineStr">
+      <c r="A291" s="7" t="inlineStr">
+        <is>
+          <t>37730</t>
+        </is>
+      </c>
+      <c r="B291" s="8" t="inlineStr">
         <is>
           <t>경상북도</t>
         </is>
       </c>
-      <c r="C291" s="4" t="inlineStr">
-        <is>
-          <t>청송군</t>
-        </is>
-      </c>
-      <c r="D291" s="3" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E291" s="4" t="inlineStr">
-        <is>
-          <t>환경관리과</t>
+      <c r="C291" s="8" t="inlineStr">
+        <is>
+          <t>영양군</t>
+        </is>
+      </c>
+      <c r="D291" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E291" s="8" t="inlineStr">
+        <is>
+          <t>농림관광국</t>
+        </is>
+      </c>
+      <c r="F291" s="5" t="inlineStr">
+        <is>
+          <t>농업축산과</t>
+        </is>
+      </c>
+      <c r="G291" s="5" t="inlineStr">
+        <is>
+          <t>유통지원과</t>
+        </is>
+      </c>
+      <c r="H291" s="5" t="inlineStr">
+        <is>
+          <t>문화관광과</t>
+        </is>
+      </c>
+      <c r="I291" s="6" t="inlineStr">
+        <is>
+          <t>산림녹지과</t>
         </is>
       </c>
     </row>
@@ -29082,86 +29509,66 @@
       </c>
       <c r="E292" s="8" t="inlineStr">
         <is>
-          <t>농림관광국</t>
+          <t>경제건설국</t>
         </is>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>농업축산과</t>
+          <t>농촌경제과</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>유통지원과</t>
+          <t>건설안전과</t>
         </is>
       </c>
       <c r="H292" s="5" t="inlineStr">
         <is>
-          <t>문화관광과</t>
+          <t>지역개발과</t>
         </is>
       </c>
       <c r="I292" s="6" t="inlineStr">
         <is>
-          <t>산림녹지과</t>
+          <t>환경보전과</t>
+        </is>
+      </c>
+      <c r="J292" s="5" t="inlineStr">
+        <is>
+          <t>양수발전건립추진단</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="7" t="inlineStr">
+      <c r="A293" s="3" t="inlineStr">
         <is>
           <t>37730</t>
         </is>
       </c>
-      <c r="B293" s="8" t="inlineStr">
+      <c r="B293" s="4" t="inlineStr">
         <is>
           <t>경상북도</t>
         </is>
       </c>
-      <c r="C293" s="8" t="inlineStr">
+      <c r="C293" s="4" t="inlineStr">
         <is>
           <t>영양군</t>
         </is>
       </c>
-      <c r="D293" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E293" s="8" t="inlineStr">
-        <is>
-          <t>경제건설국</t>
-        </is>
-      </c>
-      <c r="F293" s="5" t="inlineStr">
-        <is>
-          <t>농촌경제과</t>
-        </is>
-      </c>
-      <c r="G293" s="5" t="inlineStr">
-        <is>
-          <t>건설안전과</t>
-        </is>
-      </c>
-      <c r="H293" s="5" t="inlineStr">
-        <is>
-          <t>지역개발과</t>
-        </is>
-      </c>
-      <c r="I293" s="6" t="inlineStr">
-        <is>
-          <t>환경보전과</t>
-        </is>
-      </c>
-      <c r="J293" s="5" t="inlineStr">
-        <is>
-          <t>양수발전건립추진단</t>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E293" s="4" t="inlineStr">
+        <is>
+          <t>생태공원사업소</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>37730</t>
+          <t>37740</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
@@ -29171,7 +29578,7 @@
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>영양군</t>
+          <t>영덕군</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
@@ -29181,7 +29588,7 @@
       </c>
       <c r="E294" s="4" t="inlineStr">
         <is>
-          <t>생태공원사업소</t>
+          <t>환경위생과</t>
         </is>
       </c>
     </row>
@@ -29208,14 +29615,14 @@
       </c>
       <c r="E295" s="4" t="inlineStr">
         <is>
-          <t>환경위생과</t>
+          <t>산림과</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>37740</t>
+          <t>37750</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
@@ -29225,7 +29632,7 @@
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>영덕군</t>
+          <t>청도군</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
@@ -29235,14 +29642,44 @@
       </c>
       <c r="E296" s="4" t="inlineStr">
         <is>
-          <t>산림과</t>
+          <t>문화환경건설국</t>
+        </is>
+      </c>
+      <c r="F296" s="5" t="inlineStr">
+        <is>
+          <t>관광정책과</t>
+        </is>
+      </c>
+      <c r="G296" s="5" t="inlineStr">
+        <is>
+          <t>문화예술체육과</t>
+        </is>
+      </c>
+      <c r="H296" s="5" t="inlineStr">
+        <is>
+          <t>새마을경제과</t>
+        </is>
+      </c>
+      <c r="I296" s="6" t="inlineStr">
+        <is>
+          <t>환경산림과</t>
+        </is>
+      </c>
+      <c r="J296" s="5" t="inlineStr">
+        <is>
+          <t>건설과</t>
+        </is>
+      </c>
+      <c r="K296" s="5" t="inlineStr">
+        <is>
+          <t>미래혁신도시과</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>37750</t>
+          <t>37760</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
@@ -29252,7 +29689,7 @@
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>청도군</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
@@ -29262,37 +29699,7 @@
       </c>
       <c r="E297" s="4" t="inlineStr">
         <is>
-          <t>문화환경건설국</t>
-        </is>
-      </c>
-      <c r="F297" s="5" t="inlineStr">
-        <is>
-          <t>관광정책과</t>
-        </is>
-      </c>
-      <c r="G297" s="5" t="inlineStr">
-        <is>
-          <t>문화예술체육과</t>
-        </is>
-      </c>
-      <c r="H297" s="5" t="inlineStr">
-        <is>
-          <t>새마을경제과</t>
-        </is>
-      </c>
-      <c r="I297" s="6" t="inlineStr">
-        <is>
-          <t>환경산림과</t>
-        </is>
-      </c>
-      <c r="J297" s="5" t="inlineStr">
-        <is>
-          <t>건설과</t>
-        </is>
-      </c>
-      <c r="K297" s="5" t="inlineStr">
-        <is>
-          <t>미래혁신도시과</t>
+          <t>환경과</t>
         </is>
       </c>
     </row>
@@ -29319,14 +29726,14 @@
       </c>
       <c r="E298" s="4" t="inlineStr">
         <is>
-          <t>환경과</t>
+          <t>산림녹지과</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>37760</t>
+          <t>37770</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
@@ -29336,7 +29743,7 @@
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>성주군</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
@@ -29346,7 +29753,7 @@
       </c>
       <c r="E299" s="4" t="inlineStr">
         <is>
-          <t>산림녹지과</t>
+          <t>환경과</t>
         </is>
       </c>
     </row>
@@ -29373,41 +29780,71 @@
       </c>
       <c r="E300" s="4" t="inlineStr">
         <is>
-          <t>환경과</t>
+          <t>산림과</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="3" t="inlineStr">
-        <is>
-          <t>37770</t>
-        </is>
-      </c>
-      <c r="B301" s="4" t="inlineStr">
+      <c r="A301" s="7" t="inlineStr">
+        <is>
+          <t>37780</t>
+        </is>
+      </c>
+      <c r="B301" s="8" t="inlineStr">
         <is>
           <t>경상북도</t>
         </is>
       </c>
-      <c r="C301" s="4" t="inlineStr">
-        <is>
-          <t>성주군</t>
-        </is>
-      </c>
-      <c r="D301" s="3" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E301" s="4" t="inlineStr">
-        <is>
-          <t>산림과</t>
+      <c r="C301" s="8" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
+      <c r="D301" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E301" s="8" t="inlineStr">
+        <is>
+          <t>건설안전국</t>
+        </is>
+      </c>
+      <c r="F301" s="5" t="inlineStr">
+        <is>
+          <t>건설과</t>
+        </is>
+      </c>
+      <c r="G301" s="5" t="inlineStr">
+        <is>
+          <t>안전관리과</t>
+        </is>
+      </c>
+      <c r="H301" s="5" t="inlineStr">
+        <is>
+          <t>도시계획과</t>
+        </is>
+      </c>
+      <c r="I301" s="5" t="inlineStr">
+        <is>
+          <t>건축디자인과</t>
+        </is>
+      </c>
+      <c r="J301" s="6" t="inlineStr">
+        <is>
+          <t>환경관리과</t>
+        </is>
+      </c>
+      <c r="K301" s="6" t="inlineStr">
+        <is>
+          <t>산림녹지과</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="7" t="inlineStr">
         <is>
-          <t>37780</t>
+          <t>37790</t>
         </is>
       </c>
       <c r="B302" s="8" t="inlineStr">
@@ -29417,7 +29854,7 @@
       </c>
       <c r="C302" s="8" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>예천군</t>
         </is>
       </c>
       <c r="D302" s="7" t="inlineStr">
@@ -29427,37 +29864,32 @@
       </c>
       <c r="E302" s="8" t="inlineStr">
         <is>
-          <t>건설안전국</t>
+          <t>경제농림국</t>
         </is>
       </c>
       <c r="F302" s="5" t="inlineStr">
         <is>
-          <t>건설과</t>
+          <t>지역경제과</t>
         </is>
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>안전관리과</t>
-        </is>
-      </c>
-      <c r="H302" s="5" t="inlineStr">
-        <is>
-          <t>도시계획과</t>
+          <t>농정과</t>
+        </is>
+      </c>
+      <c r="H302" s="6" t="inlineStr">
+        <is>
+          <t>산림녹지과</t>
         </is>
       </c>
       <c r="I302" s="5" t="inlineStr">
         <is>
-          <t>건축디자인과</t>
-        </is>
-      </c>
-      <c r="J302" s="6" t="inlineStr">
-        <is>
-          <t>환경관리과</t>
-        </is>
-      </c>
-      <c r="K302" s="6" t="inlineStr">
-        <is>
-          <t>산림녹지과</t>
+          <t>축산과</t>
+        </is>
+      </c>
+      <c r="J302" s="5" t="inlineStr">
+        <is>
+          <t>농촌활력과</t>
         </is>
       </c>
     </row>
@@ -29484,84 +29916,59 @@
       </c>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>경제농림국</t>
+          <t>건설도시국</t>
         </is>
       </c>
       <c r="F303" s="5" t="inlineStr">
         <is>
-          <t>지역경제과</t>
+          <t>건설교통과</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>농정과</t>
-        </is>
-      </c>
-      <c r="H303" s="6" t="inlineStr">
-        <is>
-          <t>산림녹지과</t>
+          <t>안전재난과</t>
+        </is>
+      </c>
+      <c r="H303" s="5" t="inlineStr">
+        <is>
+          <t>도시과</t>
         </is>
       </c>
       <c r="I303" s="5" t="inlineStr">
         <is>
-          <t>축산과</t>
-        </is>
-      </c>
-      <c r="J303" s="5" t="inlineStr">
-        <is>
-          <t>농촌활력과</t>
+          <t>건축과</t>
+        </is>
+      </c>
+      <c r="J303" s="6" t="inlineStr">
+        <is>
+          <t>환경관리과</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="7" t="inlineStr">
-        <is>
-          <t>37790</t>
-        </is>
-      </c>
-      <c r="B304" s="8" t="inlineStr">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>37800</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
         <is>
           <t>경상북도</t>
         </is>
       </c>
-      <c r="C304" s="8" t="inlineStr">
-        <is>
-          <t>예천군</t>
-        </is>
-      </c>
-      <c r="D304" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E304" s="8" t="inlineStr">
-        <is>
-          <t>건설도시국</t>
-        </is>
-      </c>
-      <c r="F304" s="5" t="inlineStr">
-        <is>
-          <t>건설교통과</t>
-        </is>
-      </c>
-      <c r="G304" s="5" t="inlineStr">
-        <is>
-          <t>안전재난과</t>
-        </is>
-      </c>
-      <c r="H304" s="5" t="inlineStr">
-        <is>
-          <t>도시과</t>
-        </is>
-      </c>
-      <c r="I304" s="5" t="inlineStr">
-        <is>
-          <t>건축과</t>
-        </is>
-      </c>
-      <c r="J304" s="6" t="inlineStr">
-        <is>
-          <t>환경관리과</t>
+      <c r="C304" s="4" t="inlineStr">
+        <is>
+          <t>봉화군</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E304" s="4" t="inlineStr">
+        <is>
+          <t>녹색환경과</t>
         </is>
       </c>
     </row>
@@ -29588,86 +29995,86 @@
       </c>
       <c r="E305" s="4" t="inlineStr">
         <is>
-          <t>녹색환경과</t>
+          <t>산림소득자원과</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="3" t="inlineStr">
-        <is>
-          <t>37800</t>
-        </is>
-      </c>
-      <c r="B306" s="4" t="inlineStr">
+      <c r="A306" s="7" t="inlineStr">
+        <is>
+          <t>37810</t>
+        </is>
+      </c>
+      <c r="B306" s="8" t="inlineStr">
         <is>
           <t>경상북도</t>
         </is>
       </c>
-      <c r="C306" s="4" t="inlineStr">
-        <is>
-          <t>봉화군</t>
-        </is>
-      </c>
-      <c r="D306" s="3" t="inlineStr">
+      <c r="C306" s="8" t="inlineStr">
+        <is>
+          <t>울진군</t>
+        </is>
+      </c>
+      <c r="D306" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E306" s="8" t="inlineStr">
+        <is>
+          <t>안전건설국</t>
+        </is>
+      </c>
+      <c r="F306" s="5" t="inlineStr">
+        <is>
+          <t>안전재난과</t>
+        </is>
+      </c>
+      <c r="G306" s="6" t="inlineStr">
+        <is>
+          <t>환경위생과</t>
+        </is>
+      </c>
+      <c r="H306" s="6" t="inlineStr">
+        <is>
+          <t>산림과</t>
+        </is>
+      </c>
+      <c r="I306" s="5" t="inlineStr">
+        <is>
+          <t>도시새마을과</t>
+        </is>
+      </c>
+      <c r="J306" s="5" t="inlineStr">
+        <is>
+          <t>건설과</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t>37820</t>
+        </is>
+      </c>
+      <c r="B307" s="4" t="inlineStr">
+        <is>
+          <t>경상북도</t>
+        </is>
+      </c>
+      <c r="C307" s="4" t="inlineStr">
+        <is>
+          <t>울릉군</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="E306" s="4" t="inlineStr">
-        <is>
-          <t>산림소득자원과</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="7" t="inlineStr">
-        <is>
-          <t>37810</t>
-        </is>
-      </c>
-      <c r="B307" s="8" t="inlineStr">
-        <is>
-          <t>경상북도</t>
-        </is>
-      </c>
-      <c r="C307" s="8" t="inlineStr">
-        <is>
-          <t>울진군</t>
-        </is>
-      </c>
-      <c r="D307" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E307" s="8" t="inlineStr">
-        <is>
-          <t>안전건설국</t>
-        </is>
-      </c>
-      <c r="F307" s="5" t="inlineStr">
-        <is>
-          <t>안전재난과</t>
-        </is>
-      </c>
-      <c r="G307" s="6" t="inlineStr">
-        <is>
-          <t>환경위생과</t>
-        </is>
-      </c>
-      <c r="H307" s="6" t="inlineStr">
-        <is>
-          <t>산림과</t>
-        </is>
-      </c>
-      <c r="I307" s="5" t="inlineStr">
-        <is>
-          <t>도시새마을과</t>
-        </is>
-      </c>
-      <c r="J307" s="5" t="inlineStr">
-        <is>
-          <t>건설과</t>
+      <c r="E307" s="4" t="inlineStr">
+        <is>
+          <t>관광산림과</t>
         </is>
       </c>
     </row>
@@ -29694,14 +30101,14 @@
       </c>
       <c r="E308" s="4" t="inlineStr">
         <is>
-          <t>관광산림과</t>
+          <t>환경위생과</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t>37820</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
@@ -29709,11 +30116,7 @@
           <t>경상북도</t>
         </is>
       </c>
-      <c r="C309" s="4" t="inlineStr">
-        <is>
-          <t>울릉군</t>
-        </is>
-      </c>
+      <c r="C309" s="4" t="inlineStr"/>
       <c r="D309" s="3" t="inlineStr">
         <is>
           <t>○</t>
@@ -29721,7 +30124,27 @@
       </c>
       <c r="E309" s="4" t="inlineStr">
         <is>
-          <t>환경위생과</t>
+          <t>기후환경국</t>
+        </is>
+      </c>
+      <c r="F309" s="6" t="inlineStr">
+        <is>
+          <t>기후환경정책과</t>
+        </is>
+      </c>
+      <c r="G309" s="6" t="inlineStr">
+        <is>
+          <t>환경관리과</t>
+        </is>
+      </c>
+      <c r="H309" s="6" t="inlineStr">
+        <is>
+          <t>맑은물정책과</t>
+        </is>
+      </c>
+      <c r="I309" s="5" t="inlineStr">
+        <is>
+          <t>수자원관리과</t>
         </is>
       </c>
     </row>
@@ -29744,42 +30167,41 @@
       </c>
       <c r="E310" s="4" t="inlineStr">
         <is>
-          <t>기후환경국</t>
+          <t>산림자원국</t>
         </is>
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>기후환경정책과</t>
+          <t>산림정책과</t>
         </is>
       </c>
       <c r="G310" s="6" t="inlineStr">
         <is>
-          <t>환경관리과</t>
+          <t>산림레저관광과</t>
         </is>
       </c>
       <c r="H310" s="6" t="inlineStr">
         <is>
-          <t>맑은물정책과</t>
-        </is>
-      </c>
-      <c r="I310" s="5" t="inlineStr">
-        <is>
-          <t>수자원관리과</t>
+          <t>산림소득과</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38010</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>경상북도</t>
-        </is>
-      </c>
-      <c r="C311" s="4" t="inlineStr"/>
+          <t>경상남도</t>
+        </is>
+      </c>
+      <c r="C311" s="4" t="inlineStr">
+        <is>
+          <t>창원시</t>
+        </is>
+      </c>
       <c r="D311" s="3" t="inlineStr">
         <is>
           <t>○</t>
@@ -29787,29 +30209,34 @@
       </c>
       <c r="E311" s="4" t="inlineStr">
         <is>
-          <t>산림자원국</t>
+          <t>기후환경국</t>
         </is>
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>산림정책과</t>
+          <t>환경정책과</t>
         </is>
       </c>
       <c r="G311" s="6" t="inlineStr">
         <is>
-          <t>산림레저관광과</t>
-        </is>
-      </c>
-      <c r="H311" s="6" t="inlineStr">
-        <is>
-          <t>산림소득과</t>
+          <t>기후대기과</t>
+        </is>
+      </c>
+      <c r="H311" s="5" t="inlineStr">
+        <is>
+          <t>자원순환과</t>
+        </is>
+      </c>
+      <c r="I311" s="5" t="inlineStr">
+        <is>
+          <t>하천과</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t>38010</t>
+          <t>38020</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
@@ -29819,7 +30246,7 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
@@ -29829,34 +30256,34 @@
       </c>
       <c r="E312" s="4" t="inlineStr">
         <is>
-          <t>기후환경국</t>
+          <t>환경산림국</t>
         </is>
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>환경정책과</t>
-        </is>
-      </c>
-      <c r="G312" s="6" t="inlineStr">
-        <is>
-          <t>기후대기과</t>
-        </is>
-      </c>
-      <c r="H312" s="5" t="inlineStr">
+          <t>기후환경과</t>
+        </is>
+      </c>
+      <c r="G312" s="5" t="inlineStr">
         <is>
           <t>자원순환과</t>
         </is>
       </c>
+      <c r="H312" s="6" t="inlineStr">
+        <is>
+          <t>산림정원과</t>
+        </is>
+      </c>
       <c r="I312" s="5" t="inlineStr">
         <is>
-          <t>하천과</t>
+          <t>공원녹지과</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
         <is>
-          <t>38020</t>
+          <t>38030</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
@@ -29866,7 +30293,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>통영시</t>
         </is>
       </c>
       <c r="D313" s="3" t="inlineStr">
@@ -29876,34 +30303,39 @@
       </c>
       <c r="E313" s="4" t="inlineStr">
         <is>
-          <t>환경산림국</t>
-        </is>
-      </c>
-      <c r="F313" s="6" t="inlineStr">
-        <is>
-          <t>기후환경과</t>
+          <t>수산환경국</t>
+        </is>
+      </c>
+      <c r="F313" s="5" t="inlineStr">
+        <is>
+          <t>수산과</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
         <is>
+          <t>어업진흥과</t>
+        </is>
+      </c>
+      <c r="H313" s="5" t="inlineStr">
+        <is>
+          <t>해양산업과</t>
+        </is>
+      </c>
+      <c r="I313" s="6" t="inlineStr">
+        <is>
+          <t>환경과</t>
+        </is>
+      </c>
+      <c r="J313" s="5" t="inlineStr">
+        <is>
           <t>자원순환과</t>
-        </is>
-      </c>
-      <c r="H313" s="6" t="inlineStr">
-        <is>
-          <t>산림정원과</t>
-        </is>
-      </c>
-      <c r="I313" s="5" t="inlineStr">
-        <is>
-          <t>공원녹지과</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t>38030</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
@@ -29913,7 +30345,7 @@
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>사천시</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
@@ -29923,39 +30355,34 @@
       </c>
       <c r="E314" s="4" t="inlineStr">
         <is>
-          <t>수산환경국</t>
+          <t>복지환경국</t>
         </is>
       </c>
       <c r="F314" s="5" t="inlineStr">
         <is>
-          <t>수산과</t>
+          <t>주민돌봄과</t>
         </is>
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>어업진흥과</t>
+          <t>노인장애인과</t>
         </is>
       </c>
       <c r="H314" s="5" t="inlineStr">
         <is>
-          <t>해양산업과</t>
+          <t>여성가족과</t>
         </is>
       </c>
       <c r="I314" s="6" t="inlineStr">
         <is>
-          <t>환경과</t>
-        </is>
-      </c>
-      <c r="J314" s="5" t="inlineStr">
-        <is>
-          <t>자원순환과</t>
+          <t>환경보호과</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
         <is>
-          <t>38040</t>
+          <t>38050</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
@@ -29965,7 +30392,7 @@
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>사천시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="D315" s="3" t="inlineStr">
@@ -29975,138 +30402,143 @@
       </c>
       <c r="E315" s="4" t="inlineStr">
         <is>
-          <t>복지환경국</t>
-        </is>
-      </c>
-      <c r="F315" s="5" t="inlineStr">
-        <is>
-          <t>주민돌봄과</t>
-        </is>
-      </c>
-      <c r="G315" s="5" t="inlineStr">
-        <is>
-          <t>노인장애인과</t>
+          <t>환경국</t>
+        </is>
+      </c>
+      <c r="F315" s="6" t="inlineStr">
+        <is>
+          <t>환경정책과</t>
+        </is>
+      </c>
+      <c r="G315" s="6" t="inlineStr">
+        <is>
+          <t>기후대응과</t>
         </is>
       </c>
       <c r="H315" s="5" t="inlineStr">
         <is>
-          <t>여성가족과</t>
-        </is>
-      </c>
-      <c r="I315" s="6" t="inlineStr">
-        <is>
-          <t>환경보호과</t>
+          <t>자원순환과</t>
+        </is>
+      </c>
+      <c r="I315" s="5" t="inlineStr">
+        <is>
+          <t>하천과</t>
         </is>
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="3" t="inlineStr">
-        <is>
-          <t>38050</t>
-        </is>
-      </c>
-      <c r="B316" s="4" t="inlineStr">
+      <c r="A316" s="7" t="inlineStr">
+        <is>
+          <t>38060</t>
+        </is>
+      </c>
+      <c r="B316" s="8" t="inlineStr">
         <is>
           <t>경상남도</t>
         </is>
       </c>
-      <c r="C316" s="4" t="inlineStr">
-        <is>
-          <t>김해시</t>
-        </is>
-      </c>
-      <c r="D316" s="3" t="inlineStr">
+      <c r="C316" s="8" t="inlineStr">
+        <is>
+          <t>밀양시</t>
+        </is>
+      </c>
+      <c r="D316" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E316" s="8" t="inlineStr">
+        <is>
+          <t>나노경제국</t>
+        </is>
+      </c>
+      <c r="F316" s="5" t="inlineStr">
+        <is>
+          <t>지역경제과</t>
+        </is>
+      </c>
+      <c r="G316" s="5" t="inlineStr">
+        <is>
+          <t>나노융합과</t>
+        </is>
+      </c>
+      <c r="H316" s="5" t="inlineStr">
+        <is>
+          <t>투자유치과</t>
+        </is>
+      </c>
+      <c r="I316" s="6" t="inlineStr">
+        <is>
+          <t>환경관리과</t>
+        </is>
+      </c>
+      <c r="J316" s="5" t="inlineStr">
+        <is>
+          <t>교통행정과</t>
+        </is>
+      </c>
+      <c r="K316" s="6" t="inlineStr">
+        <is>
+          <t>산림녹지과</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="3" t="inlineStr">
+        <is>
+          <t>38070</t>
+        </is>
+      </c>
+      <c r="B317" s="4" t="inlineStr">
+        <is>
+          <t>경상남도</t>
+        </is>
+      </c>
+      <c r="C317" s="4" t="inlineStr">
+        <is>
+          <t>거제시</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="E316" s="4" t="inlineStr">
-        <is>
-          <t>환경국</t>
-        </is>
-      </c>
-      <c r="F316" s="6" t="inlineStr">
-        <is>
-          <t>환경정책과</t>
-        </is>
-      </c>
-      <c r="G316" s="6" t="inlineStr">
-        <is>
-          <t>기후대응과</t>
-        </is>
-      </c>
-      <c r="H316" s="5" t="inlineStr">
+      <c r="E317" s="4" t="inlineStr">
+        <is>
+          <t>환경녹지국</t>
+        </is>
+      </c>
+      <c r="F317" s="5" t="inlineStr">
         <is>
           <t>자원순환과</t>
         </is>
       </c>
-      <c r="I316" s="5" t="inlineStr">
-        <is>
-          <t>하천과</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="7" t="inlineStr">
-        <is>
-          <t>38060</t>
-        </is>
-      </c>
-      <c r="B317" s="8" t="inlineStr">
-        <is>
-          <t>경상남도</t>
-        </is>
-      </c>
-      <c r="C317" s="8" t="inlineStr">
-        <is>
-          <t>밀양시</t>
-        </is>
-      </c>
-      <c r="D317" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E317" s="8" t="inlineStr">
-        <is>
-          <t>나노경제국</t>
-        </is>
-      </c>
-      <c r="F317" s="5" t="inlineStr">
-        <is>
-          <t>지역경제과</t>
-        </is>
-      </c>
-      <c r="G317" s="5" t="inlineStr">
-        <is>
-          <t>나노융합과</t>
+      <c r="G317" s="6" t="inlineStr">
+        <is>
+          <t>기후환경과</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
         <is>
-          <t>투자유치과</t>
+          <t>상하수도과</t>
         </is>
       </c>
       <c r="I317" s="6" t="inlineStr">
         <is>
-          <t>환경관리과</t>
+          <t>산림과</t>
         </is>
       </c>
       <c r="J317" s="5" t="inlineStr">
         <is>
-          <t>교통행정과</t>
-        </is>
-      </c>
-      <c r="K317" s="6" t="inlineStr">
-        <is>
-          <t>산림녹지과</t>
+          <t>공원과</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t>38070</t>
+          <t>38080</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
@@ -30116,7 +30548,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>거제시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
@@ -30129,135 +30561,110 @@
           <t>환경녹지국</t>
         </is>
       </c>
-      <c r="F318" s="5" t="inlineStr">
+      <c r="F318" s="6" t="inlineStr">
+        <is>
+          <t>기후환경과</t>
+        </is>
+      </c>
+      <c r="G318" s="6" t="inlineStr">
+        <is>
+          <t>수질관리과</t>
+        </is>
+      </c>
+      <c r="H318" s="5" t="inlineStr">
         <is>
           <t>자원순환과</t>
         </is>
       </c>
-      <c r="G318" s="6" t="inlineStr">
-        <is>
-          <t>기후환경과</t>
-        </is>
-      </c>
-      <c r="H318" s="5" t="inlineStr">
-        <is>
-          <t>상하수도과</t>
-        </is>
-      </c>
-      <c r="I318" s="6" t="inlineStr">
+      <c r="I318" s="5" t="inlineStr">
+        <is>
+          <t>공원과</t>
+        </is>
+      </c>
+      <c r="J318" s="6" t="inlineStr">
         <is>
           <t>산림과</t>
         </is>
       </c>
-      <c r="J318" s="5" t="inlineStr">
-        <is>
-          <t>공원과</t>
-        </is>
-      </c>
     </row>
     <row r="319">
-      <c r="A319" s="3" t="inlineStr">
-        <is>
-          <t>38080</t>
-        </is>
-      </c>
-      <c r="B319" s="4" t="inlineStr">
+      <c r="A319" s="7" t="inlineStr">
+        <is>
+          <t>38710</t>
+        </is>
+      </c>
+      <c r="B319" s="8" t="inlineStr">
         <is>
           <t>경상남도</t>
         </is>
       </c>
-      <c r="C319" s="4" t="inlineStr">
-        <is>
-          <t>양산시</t>
-        </is>
-      </c>
-      <c r="D319" s="3" t="inlineStr">
+      <c r="C319" s="8" t="inlineStr">
+        <is>
+          <t>의령군</t>
+        </is>
+      </c>
+      <c r="D319" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E319" s="8" t="inlineStr">
+        <is>
+          <t>경제문화국</t>
+        </is>
+      </c>
+      <c r="F319" s="5" t="inlineStr">
+        <is>
+          <t>경제기업과</t>
+        </is>
+      </c>
+      <c r="G319" s="5" t="inlineStr">
+        <is>
+          <t>문화관광과</t>
+        </is>
+      </c>
+      <c r="H319" s="6" t="inlineStr">
+        <is>
+          <t>환경과</t>
+        </is>
+      </c>
+      <c r="I319" s="6" t="inlineStr">
+        <is>
+          <t>산림휴양과</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="3" t="inlineStr">
+        <is>
+          <t>38710</t>
+        </is>
+      </c>
+      <c r="B320" s="4" t="inlineStr">
+        <is>
+          <t>경상남도</t>
+        </is>
+      </c>
+      <c r="C320" s="4" t="inlineStr">
+        <is>
+          <t>의령군</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="E319" s="4" t="inlineStr">
-        <is>
-          <t>환경녹지국</t>
-        </is>
-      </c>
-      <c r="F319" s="6" t="inlineStr">
-        <is>
-          <t>기후환경과</t>
-        </is>
-      </c>
-      <c r="G319" s="6" t="inlineStr">
-        <is>
-          <t>수질관리과</t>
-        </is>
-      </c>
-      <c r="H319" s="5" t="inlineStr">
-        <is>
-          <t>자원순환과</t>
-        </is>
-      </c>
-      <c r="I319" s="5" t="inlineStr">
-        <is>
-          <t>공원과</t>
-        </is>
-      </c>
-      <c r="J319" s="6" t="inlineStr">
-        <is>
-          <t>산림과</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="7" t="inlineStr">
-        <is>
-          <t>38710</t>
-        </is>
-      </c>
-      <c r="B320" s="8" t="inlineStr">
-        <is>
-          <t>경상남도</t>
-        </is>
-      </c>
-      <c r="C320" s="8" t="inlineStr">
-        <is>
-          <t>의령군</t>
-        </is>
-      </c>
-      <c r="D320" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E320" s="8" t="inlineStr">
-        <is>
-          <t>경제문화국</t>
-        </is>
-      </c>
-      <c r="F320" s="5" t="inlineStr">
-        <is>
-          <t>경제기업과</t>
-        </is>
-      </c>
-      <c r="G320" s="5" t="inlineStr">
-        <is>
-          <t>문화관광과</t>
-        </is>
-      </c>
-      <c r="H320" s="6" t="inlineStr">
-        <is>
-          <t>환경과</t>
-        </is>
-      </c>
-      <c r="I320" s="6" t="inlineStr">
-        <is>
-          <t>산림휴양과</t>
+      <c r="E320" s="4" t="inlineStr">
+        <is>
+          <t>친환경골프장사업소</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t>38710</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
@@ -30267,7 +30674,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>의령군</t>
+          <t>함안군</t>
         </is>
       </c>
       <c r="D321" s="3" t="inlineStr">
@@ -30277,14 +30684,34 @@
       </c>
       <c r="E321" s="4" t="inlineStr">
         <is>
-          <t>친환경골프장사업소</t>
+          <t>복지환경국</t>
+        </is>
+      </c>
+      <c r="F321" s="5" t="inlineStr">
+        <is>
+          <t>복지정책과</t>
+        </is>
+      </c>
+      <c r="G321" s="5" t="inlineStr">
+        <is>
+          <t>주민복지과</t>
+        </is>
+      </c>
+      <c r="H321" s="6" t="inlineStr">
+        <is>
+          <t>환경과</t>
+        </is>
+      </c>
+      <c r="I321" s="6" t="inlineStr">
+        <is>
+          <t>산림녹지과</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
@@ -30294,7 +30721,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>함안군</t>
+          <t>창녕군</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
@@ -30304,34 +30731,39 @@
       </c>
       <c r="E322" s="4" t="inlineStr">
         <is>
-          <t>복지환경국</t>
+          <t>관광환경국</t>
         </is>
       </c>
       <c r="F322" s="5" t="inlineStr">
         <is>
-          <t>복지정책과</t>
+          <t>관광체육과</t>
         </is>
       </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
-          <t>주민복지과</t>
+          <t>문화예술과</t>
         </is>
       </c>
       <c r="H322" s="6" t="inlineStr">
         <is>
-          <t>환경과</t>
+          <t>환경위생과</t>
         </is>
       </c>
       <c r="I322" s="6" t="inlineStr">
         <is>
           <t>산림녹지과</t>
+        </is>
+      </c>
+      <c r="J322" s="6" t="inlineStr">
+        <is>
+          <t>우포생태따오기과</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>38740</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
@@ -30341,7 +30773,7 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>창녕군</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="D323" s="3" t="inlineStr">
@@ -30351,39 +30783,44 @@
       </c>
       <c r="E323" s="4" t="inlineStr">
         <is>
-          <t>관광환경국</t>
+          <t>문화환경국</t>
         </is>
       </c>
       <c r="F323" s="5" t="inlineStr">
         <is>
-          <t>관광체육과</t>
+          <t>문화예술과</t>
         </is>
       </c>
       <c r="G323" s="5" t="inlineStr">
         <is>
-          <t>문화예술과</t>
-        </is>
-      </c>
-      <c r="H323" s="6" t="inlineStr">
-        <is>
-          <t>환경위생과</t>
+          <t>관광진흥과</t>
+        </is>
+      </c>
+      <c r="H323" s="5" t="inlineStr">
+        <is>
+          <t>스포츠산업과</t>
         </is>
       </c>
       <c r="I323" s="6" t="inlineStr">
         <is>
-          <t>산림녹지과</t>
-        </is>
-      </c>
-      <c r="J323" s="6" t="inlineStr">
-        <is>
-          <t>우포생태따오기과</t>
+          <t>환경과</t>
+        </is>
+      </c>
+      <c r="J323" s="5" t="inlineStr">
+        <is>
+          <t>해양수산과</t>
+        </is>
+      </c>
+      <c r="K323" s="5" t="inlineStr">
+        <is>
+          <t>녹지공원과</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
         <is>
-          <t>38740</t>
+          <t>38750</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
@@ -30393,7 +30830,7 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>남해군</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
@@ -30403,44 +30840,44 @@
       </c>
       <c r="E324" s="4" t="inlineStr">
         <is>
-          <t>문화환경국</t>
+          <t>해양환경국</t>
         </is>
       </c>
       <c r="F324" s="5" t="inlineStr">
         <is>
-          <t>문화예술과</t>
+          <t>해양발전과</t>
         </is>
       </c>
       <c r="G324" s="5" t="inlineStr">
         <is>
-          <t>관광진흥과</t>
-        </is>
-      </c>
-      <c r="H324" s="5" t="inlineStr">
-        <is>
-          <t>스포츠산업과</t>
-        </is>
-      </c>
-      <c r="I324" s="6" t="inlineStr">
+          <t>수산자원과</t>
+        </is>
+      </c>
+      <c r="H324" s="6" t="inlineStr">
         <is>
           <t>환경과</t>
         </is>
       </c>
+      <c r="I324" s="5" t="inlineStr">
+        <is>
+          <t>재난안전과</t>
+        </is>
+      </c>
       <c r="J324" s="5" t="inlineStr">
         <is>
-          <t>해양수산과</t>
-        </is>
-      </c>
-      <c r="K324" s="5" t="inlineStr">
-        <is>
-          <t>녹지공원과</t>
+          <t>상하수도과</t>
+        </is>
+      </c>
+      <c r="K324" s="6" t="inlineStr">
+        <is>
+          <t>산림공원과</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
         <is>
-          <t>38750</t>
+          <t>38760</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
@@ -30450,7 +30887,7 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>남해군</t>
+          <t>하동군</t>
         </is>
       </c>
       <c r="D325" s="3" t="inlineStr">
@@ -30460,96 +30897,91 @@
       </c>
       <c r="E325" s="4" t="inlineStr">
         <is>
-          <t>해양환경국</t>
+          <t>문화환경국</t>
         </is>
       </c>
       <c r="F325" s="5" t="inlineStr">
         <is>
-          <t>해양발전과</t>
+          <t>문화체육과</t>
         </is>
       </c>
       <c r="G325" s="5" t="inlineStr">
         <is>
-          <t>수산자원과</t>
+          <t>관광진흥과</t>
         </is>
       </c>
       <c r="H325" s="6" t="inlineStr">
         <is>
-          <t>환경과</t>
-        </is>
-      </c>
-      <c r="I325" s="5" t="inlineStr">
-        <is>
-          <t>재난안전과</t>
+          <t>환경보호과</t>
+        </is>
+      </c>
+      <c r="I325" s="6" t="inlineStr">
+        <is>
+          <t>산림과</t>
         </is>
       </c>
       <c r="J325" s="5" t="inlineStr">
         <is>
-          <t>상하수도과</t>
-        </is>
-      </c>
-      <c r="K325" s="6" t="inlineStr">
-        <is>
-          <t>산림공원과</t>
+          <t>수도사업과</t>
         </is>
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="3" t="inlineStr">
-        <is>
-          <t>38760</t>
-        </is>
-      </c>
-      <c r="B326" s="4" t="inlineStr">
+      <c r="A326" s="7" t="inlineStr">
+        <is>
+          <t>38770</t>
+        </is>
+      </c>
+      <c r="B326" s="8" t="inlineStr">
         <is>
           <t>경상남도</t>
         </is>
       </c>
-      <c r="C326" s="4" t="inlineStr">
-        <is>
-          <t>하동군</t>
-        </is>
-      </c>
-      <c r="D326" s="3" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E326" s="4" t="inlineStr">
-        <is>
-          <t>문화환경국</t>
+      <c r="C326" s="8" t="inlineStr">
+        <is>
+          <t>산청군</t>
+        </is>
+      </c>
+      <c r="D326" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E326" s="8" t="inlineStr">
+        <is>
+          <t>항노화관광국</t>
         </is>
       </c>
       <c r="F326" s="5" t="inlineStr">
         <is>
+          <t>한방항노화과</t>
+        </is>
+      </c>
+      <c r="G326" s="5" t="inlineStr">
+        <is>
           <t>문화체육과</t>
         </is>
       </c>
-      <c r="G326" s="5" t="inlineStr">
+      <c r="H326" s="5" t="inlineStr">
         <is>
           <t>관광진흥과</t>
         </is>
       </c>
-      <c r="H326" s="6" t="inlineStr">
-        <is>
-          <t>환경보호과</t>
-        </is>
-      </c>
       <c r="I326" s="6" t="inlineStr">
         <is>
-          <t>산림과</t>
-        </is>
-      </c>
-      <c r="J326" s="5" t="inlineStr">
-        <is>
-          <t>수도사업과</t>
+          <t>산림녹지과</t>
+        </is>
+      </c>
+      <c r="J326" s="6" t="inlineStr">
+        <is>
+          <t>환경위생과</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
@@ -30559,7 +30991,7 @@
       </c>
       <c r="C327" s="8" t="inlineStr">
         <is>
-          <t>산청군</t>
+          <t>함양군</t>
         </is>
       </c>
       <c r="D327" s="7" t="inlineStr">
@@ -30569,32 +31001,32 @@
       </c>
       <c r="E327" s="8" t="inlineStr">
         <is>
-          <t>항노화관광국</t>
+          <t>경제복지국</t>
         </is>
       </c>
       <c r="F327" s="5" t="inlineStr">
         <is>
-          <t>한방항노화과</t>
+          <t>일자리경제과</t>
         </is>
       </c>
       <c r="G327" s="5" t="inlineStr">
         <is>
-          <t>문화체육과</t>
+          <t>인구정책과</t>
         </is>
       </c>
       <c r="H327" s="5" t="inlineStr">
         <is>
-          <t>관광진흥과</t>
-        </is>
-      </c>
-      <c r="I327" s="6" t="inlineStr">
-        <is>
-          <t>산림녹지과</t>
+          <t>사회복지과</t>
+        </is>
+      </c>
+      <c r="I327" s="5" t="inlineStr">
+        <is>
+          <t>노인복지과</t>
         </is>
       </c>
       <c r="J327" s="6" t="inlineStr">
         <is>
-          <t>환경위생과</t>
+          <t>환경정책과</t>
         </is>
       </c>
     </row>
@@ -30621,39 +31053,39 @@
       </c>
       <c r="E328" s="8" t="inlineStr">
         <is>
-          <t>경제복지국</t>
+          <t>안전건설국</t>
         </is>
       </c>
       <c r="F328" s="5" t="inlineStr">
         <is>
-          <t>일자리경제과</t>
+          <t>안전총괄과</t>
         </is>
       </c>
       <c r="G328" s="5" t="inlineStr">
         <is>
-          <t>인구정책과</t>
-        </is>
-      </c>
-      <c r="H328" s="5" t="inlineStr">
-        <is>
-          <t>사회복지과</t>
+          <t>도시건축과</t>
+        </is>
+      </c>
+      <c r="H328" s="6" t="inlineStr">
+        <is>
+          <t>산림녹지과</t>
         </is>
       </c>
       <c r="I328" s="5" t="inlineStr">
         <is>
-          <t>노인복지과</t>
-        </is>
-      </c>
-      <c r="J328" s="6" t="inlineStr">
-        <is>
-          <t>환경정책과</t>
+          <t>건설교통과</t>
+        </is>
+      </c>
+      <c r="J328" s="5" t="inlineStr">
+        <is>
+          <t>산삼항노화과</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>38790</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
@@ -30663,7 +31095,7 @@
       </c>
       <c r="C329" s="8" t="inlineStr">
         <is>
-          <t>함양군</t>
+          <t>거창군</t>
         </is>
       </c>
       <c r="D329" s="7" t="inlineStr">
@@ -30681,31 +31113,31 @@
           <t>안전총괄과</t>
         </is>
       </c>
-      <c r="G329" s="5" t="inlineStr">
+      <c r="G329" s="6" t="inlineStr">
+        <is>
+          <t>산림과</t>
+        </is>
+      </c>
+      <c r="H329" s="6" t="inlineStr">
+        <is>
+          <t>환경과</t>
+        </is>
+      </c>
+      <c r="I329" s="5" t="inlineStr">
+        <is>
+          <t>건설교통과</t>
+        </is>
+      </c>
+      <c r="J329" s="5" t="inlineStr">
         <is>
           <t>도시건축과</t>
-        </is>
-      </c>
-      <c r="H329" s="6" t="inlineStr">
-        <is>
-          <t>산림녹지과</t>
-        </is>
-      </c>
-      <c r="I329" s="5" t="inlineStr">
-        <is>
-          <t>건설교통과</t>
-        </is>
-      </c>
-      <c r="J329" s="5" t="inlineStr">
-        <is>
-          <t>산삼항노화과</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="7" t="inlineStr">
         <is>
-          <t>38790</t>
+          <t>38800</t>
         </is>
       </c>
       <c r="B330" s="8" t="inlineStr">
@@ -30715,7 +31147,7 @@
       </c>
       <c r="C330" s="8" t="inlineStr">
         <is>
-          <t>거창군</t>
+          <t>합천군</t>
         </is>
       </c>
       <c r="D330" s="7" t="inlineStr">
@@ -30733,88 +31165,89 @@
           <t>안전총괄과</t>
         </is>
       </c>
-      <c r="G330" s="6" t="inlineStr">
-        <is>
-          <t>산림과</t>
-        </is>
-      </c>
-      <c r="H330" s="6" t="inlineStr">
-        <is>
-          <t>환경과</t>
-        </is>
-      </c>
-      <c r="I330" s="5" t="inlineStr">
+      <c r="G330" s="5" t="inlineStr">
         <is>
           <t>건설교통과</t>
         </is>
       </c>
+      <c r="H330" s="5" t="inlineStr">
+        <is>
+          <t>도시개발허가과</t>
+        </is>
+      </c>
+      <c r="I330" s="6" t="inlineStr">
+        <is>
+          <t>환경위생과</t>
+        </is>
+      </c>
       <c r="J330" s="5" t="inlineStr">
         <is>
-          <t>도시건축과</t>
+          <t>상하수도과</t>
         </is>
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="7" t="inlineStr">
-        <is>
-          <t>38800</t>
-        </is>
-      </c>
-      <c r="B331" s="8" t="inlineStr">
+      <c r="A331" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B331" s="4" t="inlineStr">
         <is>
           <t>경상남도</t>
         </is>
       </c>
-      <c r="C331" s="8" t="inlineStr">
-        <is>
-          <t>합천군</t>
-        </is>
-      </c>
-      <c r="D331" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E331" s="8" t="inlineStr">
-        <is>
-          <t>안전건설국</t>
-        </is>
-      </c>
-      <c r="F331" s="5" t="inlineStr">
-        <is>
-          <t>안전총괄과</t>
-        </is>
-      </c>
-      <c r="G331" s="5" t="inlineStr">
-        <is>
-          <t>건설교통과</t>
-        </is>
-      </c>
-      <c r="H331" s="5" t="inlineStr">
-        <is>
-          <t>도시개발허가과</t>
-        </is>
-      </c>
-      <c r="I331" s="6" t="inlineStr">
-        <is>
-          <t>환경위생과</t>
-        </is>
-      </c>
-      <c r="J331" s="5" t="inlineStr">
-        <is>
-          <t>상하수도과</t>
+      <c r="C331" s="4" t="inlineStr"/>
+      <c r="D331" s="3" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E331" s="4" t="inlineStr">
+        <is>
+          <t>환경산림국</t>
+        </is>
+      </c>
+      <c r="F331" s="6" t="inlineStr">
+        <is>
+          <t>환경정책과</t>
+        </is>
+      </c>
+      <c r="G331" s="6" t="inlineStr">
+        <is>
+          <t>기후대기과</t>
+        </is>
+      </c>
+      <c r="H331" s="6" t="inlineStr">
+        <is>
+          <t>수질관리과</t>
+        </is>
+      </c>
+      <c r="I331" s="5" t="inlineStr">
+        <is>
+          <t>수자원과</t>
+        </is>
+      </c>
+      <c r="J331" s="6" t="inlineStr">
+        <is>
+          <t>산림관리과</t>
+        </is>
+      </c>
+      <c r="K331" s="6" t="inlineStr">
+        <is>
+          <t>산림휴양과</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>경상남도</t>
+          <t>제주특별자치도</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr"/>
@@ -30825,7 +31258,7 @@
       </c>
       <c r="E332" s="4" t="inlineStr">
         <is>
-          <t>환경산림국</t>
+          <t>기후환경국</t>
         </is>
       </c>
       <c r="F332" s="6" t="inlineStr">
@@ -30835,151 +31268,98 @@
       </c>
       <c r="G332" s="6" t="inlineStr">
         <is>
-          <t>기후대기과</t>
-        </is>
-      </c>
-      <c r="H332" s="6" t="inlineStr">
-        <is>
-          <t>수질관리과</t>
+          <t>탄소중립정책과</t>
+        </is>
+      </c>
+      <c r="H332" s="5" t="inlineStr">
+        <is>
+          <t>물정책과</t>
         </is>
       </c>
       <c r="I332" s="5" t="inlineStr">
         <is>
-          <t>수자원과</t>
+          <t>자원순환과</t>
         </is>
       </c>
       <c r="J332" s="6" t="inlineStr">
         <is>
-          <t>산림관리과</t>
-        </is>
-      </c>
-      <c r="K332" s="6" t="inlineStr">
-        <is>
-          <t>산림휴양과</t>
+          <t>산림녹지과</t>
         </is>
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="3" t="inlineStr">
+      <c r="A333" s="7" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B333" s="4" t="inlineStr">
+      <c r="B333" s="8" t="inlineStr">
         <is>
           <t>제주특별자치도</t>
         </is>
       </c>
-      <c r="C333" s="4" t="inlineStr"/>
-      <c r="D333" s="3" t="inlineStr">
+      <c r="C333" s="8" t="inlineStr"/>
+      <c r="D333" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E333" s="8" t="inlineStr">
+        <is>
+          <t>농축산식품국</t>
+        </is>
+      </c>
+      <c r="F333" s="6" t="inlineStr">
+        <is>
+          <t>친환경농업정책과</t>
+        </is>
+      </c>
+      <c r="G333" s="5" t="inlineStr">
+        <is>
+          <t>식품산업과</t>
+        </is>
+      </c>
+      <c r="H333" s="5" t="inlineStr">
+        <is>
+          <t>감귤유통과</t>
+        </is>
+      </c>
+      <c r="I333" s="6" t="inlineStr">
+        <is>
+          <t>친환경축산정책과</t>
+        </is>
+      </c>
+      <c r="J333" s="5" t="inlineStr">
+        <is>
+          <t>동물방역과</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B334" s="4" t="inlineStr">
+        <is>
+          <t>제주특별자치도</t>
+        </is>
+      </c>
+      <c r="C334" s="4" t="inlineStr"/>
+      <c r="D334" s="3" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="E333" s="4" t="inlineStr">
-        <is>
-          <t>기후환경국</t>
-        </is>
-      </c>
-      <c r="F333" s="6" t="inlineStr">
-        <is>
-          <t>환경정책과</t>
-        </is>
-      </c>
-      <c r="G333" s="6" t="inlineStr">
-        <is>
-          <t>탄소중립정책과</t>
-        </is>
-      </c>
-      <c r="H333" s="5" t="inlineStr">
-        <is>
-          <t>물정책과</t>
-        </is>
-      </c>
-      <c r="I333" s="5" t="inlineStr">
-        <is>
-          <t>자원순환과</t>
-        </is>
-      </c>
-      <c r="J333" s="6" t="inlineStr">
-        <is>
-          <t>산림녹지과</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="7" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B334" s="8" t="inlineStr">
-        <is>
-          <t>제주특별자치도</t>
-        </is>
-      </c>
-      <c r="C334" s="8" t="inlineStr"/>
-      <c r="D334" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E334" s="8" t="inlineStr">
-        <is>
-          <t>농축산식품국</t>
-        </is>
-      </c>
-      <c r="F334" s="6" t="inlineStr">
-        <is>
-          <t>친환경농업정책과</t>
-        </is>
-      </c>
-      <c r="G334" s="5" t="inlineStr">
-        <is>
-          <t>식품산업과</t>
-        </is>
-      </c>
-      <c r="H334" s="5" t="inlineStr">
-        <is>
-          <t>감귤유통과</t>
-        </is>
-      </c>
-      <c r="I334" s="6" t="inlineStr">
-        <is>
-          <t>친환경축산정책과</t>
-        </is>
-      </c>
-      <c r="J334" s="5" t="inlineStr">
-        <is>
-          <t>동물방역과</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B335" s="4" t="inlineStr">
-        <is>
-          <t>제주특별자치도</t>
-        </is>
-      </c>
-      <c r="C335" s="4" t="inlineStr"/>
-      <c r="D335" s="3" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E335" s="4" t="inlineStr">
+      <c r="E334" s="4" t="inlineStr">
         <is>
           <t>제주환경자원순환센터 [신설 2025.7.11.]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R1"/>
+  <autoFilter ref="A1:W1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
